--- a/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/Listado con punteos.xlsx
+++ b/PRACTICAS DOCENCIA/LABORATORIO MB1/LISTADO COMPLETO MACROS/Listado con punteos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\PRACTICAS DOCENCIA\LABORATORIO MB1\LISTADO COMPLETO MACROS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C950084C-D2FE-467A-8777-8264AF3A08DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59FF727-A8B3-49DA-8F2B-FE3565FB6BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B120FE9F-51A9-4E3A-8CF4-53BECC398D17}"/>
   </bookViews>
@@ -551,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -584,12 +584,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -627,9 +621,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
@@ -641,13 +632,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -659,6 +645,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3397,7 +3394,7 @@
             <v>0</v>
           </cell>
           <cell r="N66">
-            <v>0</v>
+            <v>40</v>
           </cell>
           <cell r="O66">
             <v>90</v>
@@ -4207,5358 +4204,5357 @@
   <cols>
     <col min="3" max="3" width="4.90625" customWidth="1"/>
     <col min="4" max="4" width="12.6328125" customWidth="1"/>
-    <col min="5" max="5" width="33.90625" customWidth="1"/>
-    <col min="6" max="9" width="7.453125" customWidth="1"/>
-    <col min="10" max="19" width="9.6328125" customWidth="1"/>
-    <col min="20" max="20" width="9.6328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.81640625" customWidth="1"/>
+    <col min="6" max="19" width="5.7265625" customWidth="1"/>
+    <col min="20" max="20" width="9.6328125" style="45" customWidth="1"/>
     <col min="21" max="21" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:24" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="3:24" s="1" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="52" t="s">
+    <row r="2" spans="3:24" s="1" customFormat="1" ht="130.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="J2" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="53" t="s">
+      <c r="K2" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="53" t="s">
+      <c r="L2" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="53" t="s">
+      <c r="M2" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="N2" s="53" t="s">
+      <c r="N2" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="53" t="s">
+      <c r="O2" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="53" t="s">
+      <c r="P2" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="53" t="s">
+      <c r="Q2" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="R2" s="53" t="s">
+      <c r="R2" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="S2" s="53" t="s">
+      <c r="S2" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="T2" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="U2" s="54"/>
+      <c r="U2" s="44"/>
       <c r="V2" s="4"/>
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="3:24" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27" t="s">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="29">
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="J3" s="28">
-        <v>1</v>
-      </c>
-      <c r="K3" s="29">
-        <v>1</v>
-      </c>
-      <c r="L3" s="29">
-        <v>1</v>
-      </c>
-      <c r="M3" s="29">
+      <c r="F3" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="I3" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="24">
+        <v>1</v>
+      </c>
+      <c r="K3" s="25">
+        <v>1</v>
+      </c>
+      <c r="L3" s="25">
+        <v>1</v>
+      </c>
+      <c r="M3" s="25">
         <v>1.5</v>
       </c>
-      <c r="N3" s="29">
+      <c r="N3" s="25">
         <v>2</v>
       </c>
-      <c r="O3" s="29">
+      <c r="O3" s="25">
         <v>2</v>
       </c>
-      <c r="P3" s="29">
+      <c r="P3" s="25">
         <v>2</v>
       </c>
-      <c r="Q3" s="29">
-        <v>1</v>
-      </c>
-      <c r="R3" s="29">
+      <c r="Q3" s="25">
+        <v>1</v>
+      </c>
+      <c r="R3" s="25">
         <v>1.5</v>
       </c>
-      <c r="S3" s="29">
+      <c r="S3" s="25">
         <v>5</v>
       </c>
-      <c r="T3" s="30">
+      <c r="T3" s="47">
         <f>SUM(F3:S3)</f>
         <v>20</v>
       </c>
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="3:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="31" t="s">
+      <c r="C4" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="L4" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="M4" s="33" t="s">
+      <c r="L4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="M4" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="P4" s="33" t="s">
+      <c r="P4" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="Q4" s="33" t="s">
+      <c r="Q4" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="R4" s="33" t="s">
+      <c r="R4" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="S4" s="33" t="s">
+      <c r="S4" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="T4" s="34" t="s">
+      <c r="T4" s="48" t="s">
         <v>95</v>
       </c>
       <c r="U4" s="3"/>
     </row>
     <row r="5" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C5" s="23">
-        <v>1</v>
-      </c>
-      <c r="D5" s="23">
+      <c r="C5" s="19">
+        <v>1</v>
+      </c>
+      <c r="D5" s="19">
         <v>202030174</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="31">
         <f>IF('Porcentaje de Notas'!F5="","",('Porcentaje de Notas'!F5/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="19">
         <f>IF('Porcentaje de Notas'!G5="","",('Porcentaje de Notas'!G5/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="19">
         <f>IF('Porcentaje de Notas'!H5="","",('Porcentaje de Notas'!H5/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="32">
         <f>IF('Porcentaje de Notas'!I5="","",('Porcentaje de Notas'!I5/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="31">
         <f>IF('Porcentaje de Notas'!J5="","",('Porcentaje de Notas'!J5/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="19">
         <f>IF('Porcentaje de Notas'!K5="","",('Porcentaje de Notas'!K5/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="19">
         <f>IF('Porcentaje de Notas'!L5="","",('Porcentaje de Notas'!L5/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="19">
         <f>IF('Porcentaje de Notas'!M5="","",('Porcentaje de Notas'!M5/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="19">
         <f>IF('Porcentaje de Notas'!N5="","",('Porcentaje de Notas'!N5/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="19">
         <f>IF('Porcentaje de Notas'!O5="","",('Porcentaje de Notas'!O5/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="19">
         <f>IF('Porcentaje de Notas'!P5="","",('Porcentaje de Notas'!P5/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="19">
         <f>IF('Porcentaje de Notas'!Q5="","",('Porcentaje de Notas'!Q5/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R5" s="23">
+      <c r="R5" s="19">
         <f>IF('Porcentaje de Notas'!R5="","",('Porcentaje de Notas'!R5/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S5" s="23">
+      <c r="S5" s="19">
         <f>IF('Porcentaje de Notas'!S5="","",('Porcentaje de Notas'!S5/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T5" s="37">
+      <c r="T5" s="49">
         <f>SUM(F5:S5)</f>
         <v>3.75</v>
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C6" s="23">
+      <c r="C6" s="19">
         <v>2</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="19">
         <v>202032032</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="31">
         <f>IF('Porcentaje de Notas'!F6="","",('Porcentaje de Notas'!F6/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="19">
         <f>IF('Porcentaje de Notas'!G6="","",('Porcentaje de Notas'!G6/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="19">
         <f>IF('Porcentaje de Notas'!H6="","",('Porcentaje de Notas'!H6/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="32">
         <f>IF('Porcentaje de Notas'!I6="","",('Porcentaje de Notas'!I6/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="31">
         <f>IF('Porcentaje de Notas'!J6="","",('Porcentaje de Notas'!J6/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="19">
         <f>IF('Porcentaje de Notas'!K6="","",('Porcentaje de Notas'!K6/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="19">
         <f>IF('Porcentaje de Notas'!L6="","",('Porcentaje de Notas'!L6/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="19">
         <f>IF('Porcentaje de Notas'!M6="","",('Porcentaje de Notas'!M6/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="19">
         <f>IF('Porcentaje de Notas'!N6="","",('Porcentaje de Notas'!N6/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="19">
         <f>IF('Porcentaje de Notas'!O6="","",('Porcentaje de Notas'!O6/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P6" s="23">
+      <c r="P6" s="19">
         <f>IF('Porcentaje de Notas'!P6="","",('Porcentaje de Notas'!P6/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="19">
         <f>IF('Porcentaje de Notas'!Q6="","",('Porcentaje de Notas'!Q6/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R6" s="23">
+      <c r="R6" s="19">
         <f>IF('Porcentaje de Notas'!R6="","",('Porcentaje de Notas'!R6/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S6" s="23">
+      <c r="S6" s="19">
         <f>IF('Porcentaje de Notas'!S6="","",('Porcentaje de Notas'!S6/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T6" s="37">
+      <c r="T6" s="49">
         <f t="shared" ref="T6:T69" si="0">SUM(F6:S6)</f>
         <v>18.850000000000001</v>
       </c>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C7" s="23">
+      <c r="C7" s="19">
         <v>3</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="19">
         <v>202231116</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="31">
         <f>IF('Porcentaje de Notas'!F7="","",('Porcentaje de Notas'!F7/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="19">
         <f>IF('Porcentaje de Notas'!G7="","",('Porcentaje de Notas'!G7/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="19">
         <f>IF('Porcentaje de Notas'!H7="","",('Porcentaje de Notas'!H7/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="32">
         <f>IF('Porcentaje de Notas'!I7="","",('Porcentaje de Notas'!I7/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="31">
         <f>IF('Porcentaje de Notas'!J7="","",('Porcentaje de Notas'!J7/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="19">
         <f>IF('Porcentaje de Notas'!K7="","",('Porcentaje de Notas'!K7/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="19">
         <f>IF('Porcentaje de Notas'!L7="","",('Porcentaje de Notas'!L7/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="19">
         <f>IF('Porcentaje de Notas'!M7="","",('Porcentaje de Notas'!M7/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="19">
         <f>IF('Porcentaje de Notas'!N7="","",('Porcentaje de Notas'!N7/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="19">
         <f>IF('Porcentaje de Notas'!O7="","",('Porcentaje de Notas'!O7/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="23">
+      <c r="P7" s="19">
         <f>IF('Porcentaje de Notas'!P7="","",('Porcentaje de Notas'!P7/100)*$P$3)</f>
         <v>1.7</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="19">
         <f>IF('Porcentaje de Notas'!Q7="","",('Porcentaje de Notas'!Q7/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R7" s="23">
+      <c r="R7" s="19">
         <f>IF('Porcentaje de Notas'!R7="","",('Porcentaje de Notas'!R7/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S7" s="23">
+      <c r="S7" s="19">
         <f>IF('Porcentaje de Notas'!S7="","",('Porcentaje de Notas'!S7/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T7" s="37">
+      <c r="T7" s="49">
         <f t="shared" si="0"/>
         <v>14.25</v>
       </c>
     </row>
     <row r="8" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C8" s="23">
+      <c r="C8" s="19">
         <v>4</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="19">
         <v>202330276</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="31">
         <f>IF('Porcentaje de Notas'!F8="","",('Porcentaje de Notas'!F8/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="19">
         <f>IF('Porcentaje de Notas'!G8="","",('Porcentaje de Notas'!G8/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="19">
         <f>IF('Porcentaje de Notas'!H8="","",('Porcentaje de Notas'!H8/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="32">
         <f>IF('Porcentaje de Notas'!I8="","",('Porcentaje de Notas'!I8/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="31">
         <f>IF('Porcentaje de Notas'!J8="","",('Porcentaje de Notas'!J8/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="19">
         <f>IF('Porcentaje de Notas'!K8="","",('Porcentaje de Notas'!K8/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="19">
         <f>IF('Porcentaje de Notas'!L8="","",('Porcentaje de Notas'!L8/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="19">
         <f>IF('Porcentaje de Notas'!M8="","",('Porcentaje de Notas'!M8/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="19">
         <f>IF('Porcentaje de Notas'!N8="","",('Porcentaje de Notas'!N8/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="19">
         <f>IF('Porcentaje de Notas'!O8="","",('Porcentaje de Notas'!O8/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="19">
         <f>IF('Porcentaje de Notas'!P8="","",('Porcentaje de Notas'!P8/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="19">
         <f>IF('Porcentaje de Notas'!Q8="","",('Porcentaje de Notas'!Q8/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="19">
         <f>IF('Porcentaje de Notas'!R8="","",('Porcentaje de Notas'!R8/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="19">
         <f>IF('Porcentaje de Notas'!S8="","",('Porcentaje de Notas'!S8/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T8" s="37">
+      <c r="T8" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C9" s="23">
+      <c r="C9" s="19">
         <v>5</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="19">
         <v>202331587</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="31">
         <f>IF('Porcentaje de Notas'!F9="","",('Porcentaje de Notas'!F9/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="19">
         <f>IF('Porcentaje de Notas'!G9="","",('Porcentaje de Notas'!G9/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="19">
         <f>IF('Porcentaje de Notas'!H9="","",('Porcentaje de Notas'!H9/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="32">
         <f>IF('Porcentaje de Notas'!I9="","",('Porcentaje de Notas'!I9/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="31">
         <f>IF('Porcentaje de Notas'!J9="","",('Porcentaje de Notas'!J9/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="19">
         <f>IF('Porcentaje de Notas'!K9="","",('Porcentaje de Notas'!K9/100)*$K$3)</f>
         <v>0.5</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="19">
         <f>IF('Porcentaje de Notas'!L9="","",('Porcentaje de Notas'!L9/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="19">
         <f>IF('Porcentaje de Notas'!M9="","",('Porcentaje de Notas'!M9/100)*$M$3)</f>
         <v>1.2000000000000002</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="19">
         <f>IF('Porcentaje de Notas'!N9="","",('Porcentaje de Notas'!N9/100)*$N$3)</f>
         <v>1.5</v>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="19">
         <f>IF('Porcentaje de Notas'!O9="","",('Porcentaje de Notas'!O9/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P9" s="23">
+      <c r="P9" s="19">
         <f>IF('Porcentaje de Notas'!P9="","",('Porcentaje de Notas'!P9/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="23">
+      <c r="Q9" s="19">
         <f>IF('Porcentaje de Notas'!Q9="","",('Porcentaje de Notas'!Q9/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R9" s="23">
+      <c r="R9" s="19">
         <f>IF('Porcentaje de Notas'!R9="","",('Porcentaje de Notas'!R9/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S9" s="23">
+      <c r="S9" s="19">
         <f>IF('Porcentaje de Notas'!S9="","",('Porcentaje de Notas'!S9/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T9" s="37">
+      <c r="T9" s="49">
         <f t="shared" si="0"/>
         <v>14.25</v>
       </c>
     </row>
     <row r="10" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C10" s="23">
+      <c r="C10" s="19">
         <v>6</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="19">
         <v>202332049</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="31">
         <f>IF('Porcentaje de Notas'!F10="","",('Porcentaje de Notas'!F10/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="19">
         <f>IF('Porcentaje de Notas'!G10="","",('Porcentaje de Notas'!G10/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="19">
         <f>IF('Porcentaje de Notas'!H10="","",('Porcentaje de Notas'!H10/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="32">
         <f>IF('Porcentaje de Notas'!I10="","",('Porcentaje de Notas'!I10/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="31">
         <f>IF('Porcentaje de Notas'!J10="","",('Porcentaje de Notas'!J10/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="19">
         <f>IF('Porcentaje de Notas'!K10="","",('Porcentaje de Notas'!K10/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="19">
         <f>IF('Porcentaje de Notas'!L10="","",('Porcentaje de Notas'!L10/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="19">
         <f>IF('Porcentaje de Notas'!M10="","",('Porcentaje de Notas'!M10/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="19">
         <f>IF('Porcentaje de Notas'!N10="","",('Porcentaje de Notas'!N10/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="19">
         <f>IF('Porcentaje de Notas'!O10="","",('Porcentaje de Notas'!O10/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="23">
+      <c r="P10" s="19">
         <f>IF('Porcentaje de Notas'!P10="","",('Porcentaje de Notas'!P10/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="23">
+      <c r="Q10" s="19">
         <f>IF('Porcentaje de Notas'!Q10="","",('Porcentaje de Notas'!Q10/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R10" s="23">
+      <c r="R10" s="19">
         <f>IF('Porcentaje de Notas'!R10="","",('Porcentaje de Notas'!R10/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S10" s="23">
+      <c r="S10" s="19">
         <f>IF('Porcentaje de Notas'!S10="","",('Porcentaje de Notas'!S10/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T10" s="37">
+      <c r="T10" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C11" s="23">
+      <c r="C11" s="19">
         <v>7</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="19">
         <v>202402553</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="31">
         <f>IF('Porcentaje de Notas'!F11="","",('Porcentaje de Notas'!F11/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="19">
         <f>IF('Porcentaje de Notas'!G11="","",('Porcentaje de Notas'!G11/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="19">
         <f>IF('Porcentaje de Notas'!H11="","",('Porcentaje de Notas'!H11/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="32">
         <f>IF('Porcentaje de Notas'!I11="","",('Porcentaje de Notas'!I11/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="31">
         <f>IF('Porcentaje de Notas'!J11="","",('Porcentaje de Notas'!J11/100)*$J$3)</f>
         <v>0.6</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="19">
         <f>IF('Porcentaje de Notas'!K11="","",('Porcentaje de Notas'!K11/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L11" s="19">
         <f>IF('Porcentaje de Notas'!L11="","",('Porcentaje de Notas'!L11/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="19">
         <f>IF('Porcentaje de Notas'!M11="","",('Porcentaje de Notas'!M11/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="19">
         <f>IF('Porcentaje de Notas'!N11="","",('Porcentaje de Notas'!N11/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="19">
         <f>IF('Porcentaje de Notas'!O11="","",('Porcentaje de Notas'!O11/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="23">
+      <c r="P11" s="19">
         <f>IF('Porcentaje de Notas'!P11="","",('Porcentaje de Notas'!P11/100)*$P$3)</f>
         <v>1.3</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="19">
         <f>IF('Porcentaje de Notas'!Q11="","",('Porcentaje de Notas'!Q11/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R11" s="23">
+      <c r="R11" s="19">
         <f>IF('Porcentaje de Notas'!R11="","",('Porcentaje de Notas'!R11/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S11" s="23">
+      <c r="S11" s="19">
         <f>IF('Porcentaje de Notas'!S11="","",('Porcentaje de Notas'!S11/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T11" s="37">
+      <c r="T11" s="49">
         <f t="shared" si="0"/>
         <v>9.1499999999999986</v>
       </c>
     </row>
     <row r="12" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C12" s="23">
+      <c r="C12" s="19">
         <v>8</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="19">
         <v>202430271</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="31">
         <f>IF('Porcentaje de Notas'!F12="","",('Porcentaje de Notas'!F12/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="19">
         <f>IF('Porcentaje de Notas'!G12="","",('Porcentaje de Notas'!G12/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="19">
         <f>IF('Porcentaje de Notas'!H12="","",('Porcentaje de Notas'!H12/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="32">
         <f>IF('Porcentaje de Notas'!I12="","",('Porcentaje de Notas'!I12/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="31">
         <f>IF('Porcentaje de Notas'!J12="","",('Porcentaje de Notas'!J12/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="19">
         <f>IF('Porcentaje de Notas'!K12="","",('Porcentaje de Notas'!K12/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="19">
         <f>IF('Porcentaje de Notas'!L12="","",('Porcentaje de Notas'!L12/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="19">
         <f>IF('Porcentaje de Notas'!M12="","",('Porcentaje de Notas'!M12/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="19">
         <f>IF('Porcentaje de Notas'!N12="","",('Porcentaje de Notas'!N12/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="19">
         <f>IF('Porcentaje de Notas'!O12="","",('Porcentaje de Notas'!O12/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="23">
+      <c r="P12" s="19">
         <f>IF('Porcentaje de Notas'!P12="","",('Porcentaje de Notas'!P12/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="Q12" s="19">
         <f>IF('Porcentaje de Notas'!Q12="","",('Porcentaje de Notas'!Q12/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R12" s="23">
+      <c r="R12" s="19">
         <f>IF('Porcentaje de Notas'!R12="","",('Porcentaje de Notas'!R12/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S12" s="23">
+      <c r="S12" s="19">
         <f>IF('Porcentaje de Notas'!S12="","",('Porcentaje de Notas'!S12/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T12" s="37">
+      <c r="T12" s="49">
         <f t="shared" si="0"/>
         <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C13" s="23">
+      <c r="C13" s="19">
         <v>9</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="19">
         <v>202430532</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="31">
         <f>IF('Porcentaje de Notas'!F13="","",('Porcentaje de Notas'!F13/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="19">
         <f>IF('Porcentaje de Notas'!G13="","",('Porcentaje de Notas'!G13/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="19">
         <f>IF('Porcentaje de Notas'!H13="","",('Porcentaje de Notas'!H13/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="32">
         <f>IF('Porcentaje de Notas'!I13="","",('Porcentaje de Notas'!I13/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="31">
         <f>IF('Porcentaje de Notas'!J13="","",('Porcentaje de Notas'!J13/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="19">
         <f>IF('Porcentaje de Notas'!K13="","",('Porcentaje de Notas'!K13/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="19">
         <f>IF('Porcentaje de Notas'!L13="","",('Porcentaje de Notas'!L13/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="19">
         <f>IF('Porcentaje de Notas'!M13="","",('Porcentaje de Notas'!M13/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="19">
         <f>IF('Porcentaje de Notas'!N13="","",('Porcentaje de Notas'!N13/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O13" s="23">
+      <c r="O13" s="19">
         <f>IF('Porcentaje de Notas'!O13="","",('Porcentaje de Notas'!O13/100)*$O$3)</f>
         <v>1.3</v>
       </c>
-      <c r="P13" s="23">
+      <c r="P13" s="19">
         <f>IF('Porcentaje de Notas'!P13="","",('Porcentaje de Notas'!P13/100)*$P$3)</f>
         <v>1.6</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="Q13" s="19">
         <f>IF('Porcentaje de Notas'!Q13="","",('Porcentaje de Notas'!Q13/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R13" s="23">
+      <c r="R13" s="19">
         <f>IF('Porcentaje de Notas'!R13="","",('Porcentaje de Notas'!R13/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S13" s="23">
+      <c r="S13" s="19">
         <f>IF('Porcentaje de Notas'!S13="","",('Porcentaje de Notas'!S13/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T13" s="37">
+      <c r="T13" s="49">
         <f t="shared" si="0"/>
         <v>18.399999999999999</v>
       </c>
     </row>
     <row r="14" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C14" s="23">
+      <c r="C14" s="19">
         <v>10</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="19">
         <v>202430589</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="31">
         <f>IF('Porcentaje de Notas'!F14="","",('Porcentaje de Notas'!F14/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="19">
         <f>IF('Porcentaje de Notas'!G14="","",('Porcentaje de Notas'!G14/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="19">
         <f>IF('Porcentaje de Notas'!H14="","",('Porcentaje de Notas'!H14/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="32">
         <f>IF('Porcentaje de Notas'!I14="","",('Porcentaje de Notas'!I14/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="31">
         <f>IF('Porcentaje de Notas'!J14="","",('Porcentaje de Notas'!J14/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="19">
         <f>IF('Porcentaje de Notas'!K14="","",('Porcentaje de Notas'!K14/100)*$K$3)</f>
         <v>0.9</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="19">
         <f>IF('Porcentaje de Notas'!L14="","",('Porcentaje de Notas'!L14/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="19">
         <f>IF('Porcentaje de Notas'!M14="","",('Porcentaje de Notas'!M14/100)*$M$3)</f>
         <v>1.2000000000000002</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="19">
         <f>IF('Porcentaje de Notas'!N14="","",('Porcentaje de Notas'!N14/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O14" s="23">
+      <c r="O14" s="19">
         <f>IF('Porcentaje de Notas'!O14="","",('Porcentaje de Notas'!O14/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="23">
+      <c r="P14" s="19">
         <f>IF('Porcentaje de Notas'!P14="","",('Porcentaje de Notas'!P14/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="23">
+      <c r="Q14" s="19">
         <f>IF('Porcentaje de Notas'!Q14="","",('Porcentaje de Notas'!Q14/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R14" s="23">
+      <c r="R14" s="19">
         <f>IF('Porcentaje de Notas'!R14="","",('Porcentaje de Notas'!R14/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S14" s="23">
+      <c r="S14" s="19">
         <f>IF('Porcentaje de Notas'!S14="","",('Porcentaje de Notas'!S14/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T14" s="37">
+      <c r="T14" s="49">
         <f t="shared" si="0"/>
         <v>10.75</v>
       </c>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C15" s="23">
+      <c r="C15" s="19">
         <v>11</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="19">
         <v>202430602</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="31">
         <f>IF('Porcentaje de Notas'!F15="","",('Porcentaje de Notas'!F15/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="19">
         <f>IF('Porcentaje de Notas'!G15="","",('Porcentaje de Notas'!G15/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="19">
         <f>IF('Porcentaje de Notas'!H15="","",('Porcentaje de Notas'!H15/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="32">
         <f>IF('Porcentaje de Notas'!I15="","",('Porcentaje de Notas'!I15/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="31">
         <f>IF('Porcentaje de Notas'!J15="","",('Porcentaje de Notas'!J15/100)*$J$3)</f>
         <v>0.6</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="19">
         <f>IF('Porcentaje de Notas'!K15="","",('Porcentaje de Notas'!K15/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="19">
         <f>IF('Porcentaje de Notas'!L15="","",('Porcentaje de Notas'!L15/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="19">
         <f>IF('Porcentaje de Notas'!M15="","",('Porcentaje de Notas'!M15/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="19">
         <f>IF('Porcentaje de Notas'!N15="","",('Porcentaje de Notas'!N15/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O15" s="23">
+      <c r="O15" s="19">
         <f>IF('Porcentaje de Notas'!O15="","",('Porcentaje de Notas'!O15/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="23">
+      <c r="P15" s="19">
         <f>IF('Porcentaje de Notas'!P15="","",('Porcentaje de Notas'!P15/100)*$P$3)</f>
         <v>0.6</v>
       </c>
-      <c r="Q15" s="23">
+      <c r="Q15" s="19">
         <f>IF('Porcentaje de Notas'!Q15="","",('Porcentaje de Notas'!Q15/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R15" s="23">
+      <c r="R15" s="19">
         <f>IF('Porcentaje de Notas'!R15="","",('Porcentaje de Notas'!R15/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S15" s="23">
+      <c r="S15" s="19">
         <f>IF('Porcentaje de Notas'!S15="","",('Porcentaje de Notas'!S15/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T15" s="37">
+      <c r="T15" s="49">
         <f t="shared" si="0"/>
         <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="16" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C16" s="23">
+      <c r="C16" s="19">
         <v>12</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="19">
         <v>202430633</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="31">
         <f>IF('Porcentaje de Notas'!F16="","",('Porcentaje de Notas'!F16/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="19">
         <f>IF('Porcentaje de Notas'!G16="","",('Porcentaje de Notas'!G16/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="19">
         <f>IF('Porcentaje de Notas'!H16="","",('Porcentaje de Notas'!H16/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="32">
         <f>IF('Porcentaje de Notas'!I16="","",('Porcentaje de Notas'!I16/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="31">
         <f>IF('Porcentaje de Notas'!J16="","",('Porcentaje de Notas'!J16/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="19">
         <f>IF('Porcentaje de Notas'!K16="","",('Porcentaje de Notas'!K16/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L16" s="23">
+      <c r="L16" s="19">
         <f>IF('Porcentaje de Notas'!L16="","",('Porcentaje de Notas'!L16/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M16" s="23">
+      <c r="M16" s="19">
         <f>IF('Porcentaje de Notas'!M16="","",('Porcentaje de Notas'!M16/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N16" s="23">
+      <c r="N16" s="19">
         <f>IF('Porcentaje de Notas'!N16="","",('Porcentaje de Notas'!N16/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O16" s="23">
+      <c r="O16" s="19">
         <f>IF('Porcentaje de Notas'!O16="","",('Porcentaje de Notas'!O16/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P16" s="23">
+      <c r="P16" s="19">
         <f>IF('Porcentaje de Notas'!P16="","",('Porcentaje de Notas'!P16/100)*$P$3)</f>
         <v>1</v>
       </c>
-      <c r="Q16" s="23">
+      <c r="Q16" s="19">
         <f>IF('Porcentaje de Notas'!Q16="","",('Porcentaje de Notas'!Q16/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R16" s="23">
+      <c r="R16" s="19">
         <f>IF('Porcentaje de Notas'!R16="","",('Porcentaje de Notas'!R16/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S16" s="23">
+      <c r="S16" s="19">
         <f>IF('Porcentaje de Notas'!S16="","",('Porcentaje de Notas'!S16/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T16" s="37">
+      <c r="T16" s="49">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C17" s="23">
+      <c r="C17" s="19">
         <v>13</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="19">
         <v>202430645</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="31">
         <f>IF('Porcentaje de Notas'!F17="","",('Porcentaje de Notas'!F17/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="19">
         <f>IF('Porcentaje de Notas'!G17="","",('Porcentaje de Notas'!G17/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="19">
         <f>IF('Porcentaje de Notas'!H17="","",('Porcentaje de Notas'!H17/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="32">
         <f>IF('Porcentaje de Notas'!I17="","",('Porcentaje de Notas'!I17/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="31">
         <f>IF('Porcentaje de Notas'!J17="","",('Porcentaje de Notas'!J17/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="19">
         <f>IF('Porcentaje de Notas'!K17="","",('Porcentaje de Notas'!K17/100)*$K$3)</f>
         <v>0.85</v>
       </c>
-      <c r="L17" s="23">
+      <c r="L17" s="19">
         <f>IF('Porcentaje de Notas'!L17="","",('Porcentaje de Notas'!L17/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M17" s="23">
+      <c r="M17" s="19">
         <f>IF('Porcentaje de Notas'!M17="","",('Porcentaje de Notas'!M17/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N17" s="23">
+      <c r="N17" s="19">
         <f>IF('Porcentaje de Notas'!N17="","",('Porcentaje de Notas'!N17/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O17" s="23">
+      <c r="O17" s="19">
         <f>IF('Porcentaje de Notas'!O17="","",('Porcentaje de Notas'!O17/100)*$O$3)</f>
         <v>1.5</v>
       </c>
-      <c r="P17" s="23">
+      <c r="P17" s="19">
         <f>IF('Porcentaje de Notas'!P17="","",('Porcentaje de Notas'!P17/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q17" s="23">
+      <c r="Q17" s="19">
         <f>IF('Porcentaje de Notas'!Q17="","",('Porcentaje de Notas'!Q17/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R17" s="23">
+      <c r="R17" s="19">
         <f>IF('Porcentaje de Notas'!R17="","",('Porcentaje de Notas'!R17/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S17" s="23">
+      <c r="S17" s="19">
         <f>IF('Porcentaje de Notas'!S17="","",('Porcentaje de Notas'!S17/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T17" s="37">
+      <c r="T17" s="49">
         <f t="shared" si="0"/>
         <v>17.350000000000001</v>
       </c>
     </row>
     <row r="18" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C18" s="23">
+      <c r="C18" s="19">
         <v>14</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="19">
         <v>202430733</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="31">
         <f>IF('Porcentaje de Notas'!F18="","",('Porcentaje de Notas'!F18/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="19">
         <f>IF('Porcentaje de Notas'!G18="","",('Porcentaje de Notas'!G18/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="19">
         <f>IF('Porcentaje de Notas'!H18="","",('Porcentaje de Notas'!H18/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I18" s="36">
+      <c r="I18" s="32">
         <f>IF('Porcentaje de Notas'!I18="","",('Porcentaje de Notas'!I18/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="31">
         <f>IF('Porcentaje de Notas'!J18="","",('Porcentaje de Notas'!J18/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="19">
         <f>IF('Porcentaje de Notas'!K18="","",('Porcentaje de Notas'!K18/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="19">
         <f>IF('Porcentaje de Notas'!L18="","",('Porcentaje de Notas'!L18/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="19">
         <f>IF('Porcentaje de Notas'!M18="","",('Porcentaje de Notas'!M18/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="19">
         <f>IF('Porcentaje de Notas'!N18="","",('Porcentaje de Notas'!N18/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O18" s="23">
+      <c r="O18" s="19">
         <f>IF('Porcentaje de Notas'!O18="","",('Porcentaje de Notas'!O18/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P18" s="23">
+      <c r="P18" s="19">
         <f>IF('Porcentaje de Notas'!P18="","",('Porcentaje de Notas'!P18/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q18" s="23">
+      <c r="Q18" s="19">
         <f>IF('Porcentaje de Notas'!Q18="","",('Porcentaje de Notas'!Q18/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R18" s="23">
+      <c r="R18" s="19">
         <f>IF('Porcentaje de Notas'!R18="","",('Porcentaje de Notas'!R18/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S18" s="23">
+      <c r="S18" s="19">
         <f>IF('Porcentaje de Notas'!S18="","",('Porcentaje de Notas'!S18/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T18" s="37">
+      <c r="T18" s="49">
         <f t="shared" si="0"/>
         <v>18.100000000000001</v>
       </c>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C19" s="23">
+      <c r="C19" s="19">
         <v>15</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="19">
         <v>202430804</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="31">
         <f>IF('Porcentaje de Notas'!F19="","",('Porcentaje de Notas'!F19/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="19">
         <f>IF('Porcentaje de Notas'!G19="","",('Porcentaje de Notas'!G19/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="19">
         <f>IF('Porcentaje de Notas'!H19="","",('Porcentaje de Notas'!H19/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="36">
+      <c r="I19" s="32">
         <f>IF('Porcentaje de Notas'!I19="","",('Porcentaje de Notas'!I19/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="31">
         <f>IF('Porcentaje de Notas'!J19="","",('Porcentaje de Notas'!J19/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="19">
         <f>IF('Porcentaje de Notas'!K19="","",('Porcentaje de Notas'!K19/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L19" s="23">
+      <c r="L19" s="19">
         <f>IF('Porcentaje de Notas'!L19="","",('Porcentaje de Notas'!L19/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="19">
         <f>IF('Porcentaje de Notas'!M19="","",('Porcentaje de Notas'!M19/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="19">
         <f>IF('Porcentaje de Notas'!N19="","",('Porcentaje de Notas'!N19/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O19" s="23">
+      <c r="O19" s="19">
         <f>IF('Porcentaje de Notas'!O19="","",('Porcentaje de Notas'!O19/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P19" s="23">
+      <c r="P19" s="19">
         <f>IF('Porcentaje de Notas'!P19="","",('Porcentaje de Notas'!P19/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q19" s="23">
+      <c r="Q19" s="19">
         <f>IF('Porcentaje de Notas'!Q19="","",('Porcentaje de Notas'!Q19/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R19" s="23">
+      <c r="R19" s="19">
         <f>IF('Porcentaje de Notas'!R19="","",('Porcentaje de Notas'!R19/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S19" s="23">
+      <c r="S19" s="19">
         <f>IF('Porcentaje de Notas'!S19="","",('Porcentaje de Notas'!S19/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T19" s="37">
+      <c r="T19" s="49">
         <f t="shared" si="0"/>
         <v>10.6</v>
       </c>
     </row>
     <row r="20" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C20" s="23">
+      <c r="C20" s="19">
         <v>16</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="19">
         <v>202430829</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="31">
         <f>IF('Porcentaje de Notas'!F20="","",('Porcentaje de Notas'!F20/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="19">
         <f>IF('Porcentaje de Notas'!G20="","",('Porcentaje de Notas'!G20/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="19">
         <f>IF('Porcentaje de Notas'!H20="","",('Porcentaje de Notas'!H20/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I20" s="36">
+      <c r="I20" s="32">
         <f>IF('Porcentaje de Notas'!I20="","",('Porcentaje de Notas'!I20/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="31">
         <f>IF('Porcentaje de Notas'!J20="","",('Porcentaje de Notas'!J20/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="19">
         <f>IF('Porcentaje de Notas'!K20="","",('Porcentaje de Notas'!K20/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L20" s="23">
+      <c r="L20" s="19">
         <f>IF('Porcentaje de Notas'!L20="","",('Porcentaje de Notas'!L20/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M20" s="23">
+      <c r="M20" s="19">
         <f>IF('Porcentaje de Notas'!M20="","",('Porcentaje de Notas'!M20/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N20" s="23">
+      <c r="N20" s="19">
         <f>IF('Porcentaje de Notas'!N20="","",('Porcentaje de Notas'!N20/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O20" s="23">
+      <c r="O20" s="19">
         <f>IF('Porcentaje de Notas'!O20="","",('Porcentaje de Notas'!O20/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P20" s="23">
+      <c r="P20" s="19">
         <f>IF('Porcentaje de Notas'!P20="","",('Porcentaje de Notas'!P20/100)*$P$3)</f>
         <v>1.7</v>
       </c>
-      <c r="Q20" s="23">
+      <c r="Q20" s="19">
         <f>IF('Porcentaje de Notas'!Q20="","",('Porcentaje de Notas'!Q20/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R20" s="23">
+      <c r="R20" s="19">
         <f>IF('Porcentaje de Notas'!R20="","",('Porcentaje de Notas'!R20/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S20" s="23">
+      <c r="S20" s="19">
         <f>IF('Porcentaje de Notas'!S20="","",('Porcentaje de Notas'!S20/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T20" s="37">
+      <c r="T20" s="49">
         <f t="shared" si="0"/>
         <v>18.399999999999999</v>
       </c>
     </row>
     <row r="21" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C21" s="23">
+      <c r="C21" s="19">
         <v>17</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="19">
         <v>202431169</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="31">
         <f>IF('Porcentaje de Notas'!F21="","",('Porcentaje de Notas'!F21/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="19">
         <f>IF('Porcentaje de Notas'!G21="","",('Porcentaje de Notas'!G21/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="19">
         <f>IF('Porcentaje de Notas'!H21="","",('Porcentaje de Notas'!H21/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="32">
         <f>IF('Porcentaje de Notas'!I21="","",('Porcentaje de Notas'!I21/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="31">
         <f>IF('Porcentaje de Notas'!J21="","",('Porcentaje de Notas'!J21/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="19">
         <f>IF('Porcentaje de Notas'!K21="","",('Porcentaje de Notas'!K21/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L21" s="23">
+      <c r="L21" s="19">
         <f>IF('Porcentaje de Notas'!L21="","",('Porcentaje de Notas'!L21/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M21" s="23">
+      <c r="M21" s="19">
         <f>IF('Porcentaje de Notas'!M21="","",('Porcentaje de Notas'!M21/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="19">
         <f>IF('Porcentaje de Notas'!N21="","",('Porcentaje de Notas'!N21/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O21" s="23">
+      <c r="O21" s="19">
         <f>IF('Porcentaje de Notas'!O21="","",('Porcentaje de Notas'!O21/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P21" s="23">
+      <c r="P21" s="19">
         <f>IF('Porcentaje de Notas'!P21="","",('Porcentaje de Notas'!P21/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q21" s="23">
+      <c r="Q21" s="19">
         <f>IF('Porcentaje de Notas'!Q21="","",('Porcentaje de Notas'!Q21/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R21" s="23">
+      <c r="R21" s="19">
         <f>IF('Porcentaje de Notas'!R21="","",('Porcentaje de Notas'!R21/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S21" s="23">
+      <c r="S21" s="19">
         <f>IF('Porcentaje de Notas'!S21="","",('Porcentaje de Notas'!S21/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T21" s="37">
+      <c r="T21" s="49">
         <f t="shared" si="0"/>
         <v>18.100000000000001</v>
       </c>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C22" s="23">
+      <c r="C22" s="19">
         <v>18</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="19">
         <v>202431502</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="31">
         <f>IF('Porcentaje de Notas'!F22="","",('Porcentaje de Notas'!F22/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="19">
         <f>IF('Porcentaje de Notas'!G22="","",('Porcentaje de Notas'!G22/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="19">
         <f>IF('Porcentaje de Notas'!H22="","",('Porcentaje de Notas'!H22/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="32">
         <f>IF('Porcentaje de Notas'!I22="","",('Porcentaje de Notas'!I22/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="31">
         <f>IF('Porcentaje de Notas'!J22="","",('Porcentaje de Notas'!J22/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K22" s="23">
+      <c r="K22" s="19">
         <f>IF('Porcentaje de Notas'!K22="","",('Porcentaje de Notas'!K22/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L22" s="23">
+      <c r="L22" s="19">
         <f>IF('Porcentaje de Notas'!L22="","",('Porcentaje de Notas'!L22/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M22" s="23">
+      <c r="M22" s="19">
         <f>IF('Porcentaje de Notas'!M22="","",('Porcentaje de Notas'!M22/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N22" s="23">
+      <c r="N22" s="19">
         <f>IF('Porcentaje de Notas'!N22="","",('Porcentaje de Notas'!N22/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O22" s="23">
+      <c r="O22" s="19">
         <f>IF('Porcentaje de Notas'!O22="","",('Porcentaje de Notas'!O22/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P22" s="23">
+      <c r="P22" s="19">
         <f>IF('Porcentaje de Notas'!P22="","",('Porcentaje de Notas'!P22/100)*$P$3)</f>
         <v>0.9</v>
       </c>
-      <c r="Q22" s="23">
+      <c r="Q22" s="19">
         <f>IF('Porcentaje de Notas'!Q22="","",('Porcentaje de Notas'!Q22/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R22" s="23">
+      <c r="R22" s="19">
         <f>IF('Porcentaje de Notas'!R22="","",('Porcentaje de Notas'!R22/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S22" s="23">
+      <c r="S22" s="19">
         <f>IF('Porcentaje de Notas'!S22="","",('Porcentaje de Notas'!S22/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T22" s="37">
+      <c r="T22" s="49">
         <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
     </row>
     <row r="23" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C23" s="23">
+      <c r="C23" s="19">
         <v>19</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="19">
         <v>202431726</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="31">
         <f>IF('Porcentaje de Notas'!F23="","",('Porcentaje de Notas'!F23/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="19">
         <f>IF('Porcentaje de Notas'!G23="","",('Porcentaje de Notas'!G23/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="19">
         <f>IF('Porcentaje de Notas'!H23="","",('Porcentaje de Notas'!H23/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="32">
         <f>IF('Porcentaje de Notas'!I23="","",('Porcentaje de Notas'!I23/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="31">
         <f>IF('Porcentaje de Notas'!J23="","",('Porcentaje de Notas'!J23/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="19">
         <f>IF('Porcentaje de Notas'!K23="","",('Porcentaje de Notas'!K23/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L23" s="23">
+      <c r="L23" s="19">
         <f>IF('Porcentaje de Notas'!L23="","",('Porcentaje de Notas'!L23/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M23" s="23">
+      <c r="M23" s="19">
         <f>IF('Porcentaje de Notas'!M23="","",('Porcentaje de Notas'!M23/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N23" s="23">
+      <c r="N23" s="19">
         <f>IF('Porcentaje de Notas'!N23="","",('Porcentaje de Notas'!N23/100)*$N$3)</f>
         <v>1.8</v>
       </c>
-      <c r="O23" s="23">
+      <c r="O23" s="19">
         <f>IF('Porcentaje de Notas'!O23="","",('Porcentaje de Notas'!O23/100)*$O$3)</f>
         <v>1.9</v>
       </c>
-      <c r="P23" s="23">
+      <c r="P23" s="19">
         <f>IF('Porcentaje de Notas'!P23="","",('Porcentaje de Notas'!P23/100)*$P$3)</f>
         <v>1.8</v>
       </c>
-      <c r="Q23" s="23">
+      <c r="Q23" s="19">
         <f>IF('Porcentaje de Notas'!Q23="","",('Porcentaje de Notas'!Q23/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R23" s="23">
+      <c r="R23" s="19">
         <f>IF('Porcentaje de Notas'!R23="","",('Porcentaje de Notas'!R23/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S23" s="23">
+      <c r="S23" s="19">
         <f>IF('Porcentaje de Notas'!S23="","",('Porcentaje de Notas'!S23/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T23" s="37">
+      <c r="T23" s="49">
         <f t="shared" si="0"/>
         <v>11.25</v>
       </c>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C24" s="23">
+      <c r="C24" s="19">
         <v>20</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="19">
         <v>202431817</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="31">
         <f>IF('Porcentaje de Notas'!F24="","",('Porcentaje de Notas'!F24/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="19">
         <f>IF('Porcentaje de Notas'!G24="","",('Porcentaje de Notas'!G24/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="19">
         <f>IF('Porcentaje de Notas'!H24="","",('Porcentaje de Notas'!H24/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I24" s="36">
+      <c r="I24" s="32">
         <f>IF('Porcentaje de Notas'!I24="","",('Porcentaje de Notas'!I24/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="31">
         <f>IF('Porcentaje de Notas'!J24="","",('Porcentaje de Notas'!J24/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K24" s="23">
+      <c r="K24" s="19">
         <f>IF('Porcentaje de Notas'!K24="","",('Porcentaje de Notas'!K24/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L24" s="23">
+      <c r="L24" s="19">
         <f>IF('Porcentaje de Notas'!L24="","",('Porcentaje de Notas'!L24/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M24" s="23">
+      <c r="M24" s="19">
         <f>IF('Porcentaje de Notas'!M24="","",('Porcentaje de Notas'!M24/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="23">
+      <c r="N24" s="19">
         <f>IF('Porcentaje de Notas'!N24="","",('Porcentaje de Notas'!N24/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="23">
+      <c r="O24" s="19">
         <f>IF('Porcentaje de Notas'!O24="","",('Porcentaje de Notas'!O24/100)*$O$3)</f>
         <v>0.3</v>
       </c>
-      <c r="P24" s="23">
+      <c r="P24" s="19">
         <f>IF('Porcentaje de Notas'!P24="","",('Porcentaje de Notas'!P24/100)*$P$3)</f>
         <v>1.8</v>
       </c>
-      <c r="Q24" s="23">
+      <c r="Q24" s="19">
         <f>IF('Porcentaje de Notas'!Q24="","",('Porcentaje de Notas'!Q24/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R24" s="23">
+      <c r="R24" s="19">
         <f>IF('Porcentaje de Notas'!R24="","",('Porcentaje de Notas'!R24/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S24" s="23">
+      <c r="S24" s="19">
         <f>IF('Porcentaje de Notas'!S24="","",('Porcentaje de Notas'!S24/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T24" s="37">
+      <c r="T24" s="49">
         <f t="shared" si="0"/>
         <v>10.1</v>
       </c>
     </row>
     <row r="25" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C25" s="23">
+      <c r="C25" s="19">
         <v>21</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="19">
         <v>202431819</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="31">
         <f>IF('Porcentaje de Notas'!F25="","",('Porcentaje de Notas'!F25/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="19">
         <f>IF('Porcentaje de Notas'!G25="","",('Porcentaje de Notas'!G25/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="19">
         <f>IF('Porcentaje de Notas'!H25="","",('Porcentaje de Notas'!H25/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="32">
         <f>IF('Porcentaje de Notas'!I25="","",('Porcentaje de Notas'!I25/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="31">
         <f>IF('Porcentaje de Notas'!J25="","",('Porcentaje de Notas'!J25/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="23">
+      <c r="K25" s="19">
         <f>IF('Porcentaje de Notas'!K25="","",('Porcentaje de Notas'!K25/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L25" s="23">
+      <c r="L25" s="19">
         <f>IF('Porcentaje de Notas'!L25="","",('Porcentaje de Notas'!L25/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M25" s="23">
+      <c r="M25" s="19">
         <f>IF('Porcentaje de Notas'!M25="","",('Porcentaje de Notas'!M25/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N25" s="23">
+      <c r="N25" s="19">
         <f>IF('Porcentaje de Notas'!N25="","",('Porcentaje de Notas'!N25/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="23">
+      <c r="O25" s="19">
         <f>IF('Porcentaje de Notas'!O25="","",('Porcentaje de Notas'!O25/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P25" s="23">
+      <c r="P25" s="19">
         <f>IF('Porcentaje de Notas'!P25="","",('Porcentaje de Notas'!P25/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q25" s="23">
+      <c r="Q25" s="19">
         <f>IF('Porcentaje de Notas'!Q25="","",('Porcentaje de Notas'!Q25/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R25" s="23">
+      <c r="R25" s="19">
         <f>IF('Porcentaje de Notas'!R25="","",('Porcentaje de Notas'!R25/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S25" s="23">
+      <c r="S25" s="19">
         <f>IF('Porcentaje de Notas'!S25="","",('Porcentaje de Notas'!S25/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T25" s="37">
+      <c r="T25" s="49">
         <f t="shared" si="0"/>
         <v>13.399999999999999</v>
       </c>
     </row>
     <row r="26" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C26" s="23">
+      <c r="C26" s="19">
         <v>22</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="19">
         <v>202431863</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="31">
         <f>IF('Porcentaje de Notas'!F26="","",('Porcentaje de Notas'!F26/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="19">
         <f>IF('Porcentaje de Notas'!G26="","",('Porcentaje de Notas'!G26/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="19">
         <f>IF('Porcentaje de Notas'!H26="","",('Porcentaje de Notas'!H26/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="36">
+      <c r="I26" s="32">
         <f>IF('Porcentaje de Notas'!I26="","",('Porcentaje de Notas'!I26/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="31">
         <f>IF('Porcentaje de Notas'!J26="","",('Porcentaje de Notas'!J26/100)*$J$3)</f>
         <v>0.5</v>
       </c>
-      <c r="K26" s="23">
+      <c r="K26" s="19">
         <f>IF('Porcentaje de Notas'!K26="","",('Porcentaje de Notas'!K26/100)*$K$3)</f>
         <v>0.5</v>
       </c>
-      <c r="L26" s="23">
+      <c r="L26" s="19">
         <f>IF('Porcentaje de Notas'!L26="","",('Porcentaje de Notas'!L26/100)*$L$3)</f>
         <v>0.5</v>
       </c>
-      <c r="M26" s="23">
+      <c r="M26" s="19">
         <f>IF('Porcentaje de Notas'!M26="","",('Porcentaje de Notas'!M26/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N26" s="23">
+      <c r="N26" s="19">
         <f>IF('Porcentaje de Notas'!N26="","",('Porcentaje de Notas'!N26/100)*$N$3)</f>
         <v>0.5</v>
       </c>
-      <c r="O26" s="23">
+      <c r="O26" s="19">
         <f>IF('Porcentaje de Notas'!O26="","",('Porcentaje de Notas'!O26/100)*$O$3)</f>
         <v>0.5</v>
       </c>
-      <c r="P26" s="23">
+      <c r="P26" s="19">
         <f>IF('Porcentaje de Notas'!P26="","",('Porcentaje de Notas'!P26/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q26" s="23">
+      <c r="Q26" s="19">
         <f>IF('Porcentaje de Notas'!Q26="","",('Porcentaje de Notas'!Q26/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R26" s="23">
+      <c r="R26" s="19">
         <f>IF('Porcentaje de Notas'!R26="","",('Porcentaje de Notas'!R26/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S26" s="23">
+      <c r="S26" s="19">
         <f>IF('Porcentaje de Notas'!S26="","",('Porcentaje de Notas'!S26/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T26" s="37">
+      <c r="T26" s="49">
         <f t="shared" si="0"/>
         <v>12.8</v>
       </c>
     </row>
     <row r="27" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C27" s="23">
+      <c r="C27" s="19">
         <v>23</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="19">
         <v>202432080</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="31">
         <f>IF('Porcentaje de Notas'!F27="","",('Porcentaje de Notas'!F27/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="19">
         <f>IF('Porcentaje de Notas'!G27="","",('Porcentaje de Notas'!G27/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="19">
         <f>IF('Porcentaje de Notas'!H27="","",('Porcentaje de Notas'!H27/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="36">
+      <c r="I27" s="32">
         <f>IF('Porcentaje de Notas'!I27="","",('Porcentaje de Notas'!I27/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="31">
         <f>IF('Porcentaje de Notas'!J27="","",('Porcentaje de Notas'!J27/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="19">
         <f>IF('Porcentaje de Notas'!K27="","",('Porcentaje de Notas'!K27/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L27" s="23">
+      <c r="L27" s="19">
         <f>IF('Porcentaje de Notas'!L27="","",('Porcentaje de Notas'!L27/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M27" s="23">
+      <c r="M27" s="19">
         <f>IF('Porcentaje de Notas'!M27="","",('Porcentaje de Notas'!M27/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N27" s="23">
+      <c r="N27" s="19">
         <f>IF('Porcentaje de Notas'!N27="","",('Porcentaje de Notas'!N27/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O27" s="23">
+      <c r="O27" s="19">
         <f>IF('Porcentaje de Notas'!O27="","",('Porcentaje de Notas'!O27/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P27" s="23">
+      <c r="P27" s="19">
         <f>IF('Porcentaje de Notas'!P27="","",('Porcentaje de Notas'!P27/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q27" s="23">
+      <c r="Q27" s="19">
         <f>IF('Porcentaje de Notas'!Q27="","",('Porcentaje de Notas'!Q27/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R27" s="23">
+      <c r="R27" s="19">
         <f>IF('Porcentaje de Notas'!R27="","",('Porcentaje de Notas'!R27/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S27" s="23">
+      <c r="S27" s="19">
         <f>IF('Porcentaje de Notas'!S27="","",('Porcentaje de Notas'!S27/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T27" s="37">
+      <c r="T27" s="49">
         <f t="shared" si="0"/>
         <v>9.4</v>
       </c>
     </row>
     <row r="28" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C28" s="23">
+      <c r="C28" s="19">
         <v>24</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="19">
         <v>202432085</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="31">
         <f>IF('Porcentaje de Notas'!F28="","",('Porcentaje de Notas'!F28/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="19">
         <f>IF('Porcentaje de Notas'!G28="","",('Porcentaje de Notas'!G28/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="19">
         <f>IF('Porcentaje de Notas'!H28="","",('Porcentaje de Notas'!H28/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I28" s="36">
+      <c r="I28" s="32">
         <f>IF('Porcentaje de Notas'!I28="","",('Porcentaje de Notas'!I28/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="31">
         <f>IF('Porcentaje de Notas'!J28="","",('Porcentaje de Notas'!J28/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K28" s="23">
+      <c r="K28" s="19">
         <f>IF('Porcentaje de Notas'!K28="","",('Porcentaje de Notas'!K28/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L28" s="23">
+      <c r="L28" s="19">
         <f>IF('Porcentaje de Notas'!L28="","",('Porcentaje de Notas'!L28/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M28" s="23">
+      <c r="M28" s="19">
         <f>IF('Porcentaje de Notas'!M28="","",('Porcentaje de Notas'!M28/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N28" s="23">
+      <c r="N28" s="19">
         <f>IF('Porcentaje de Notas'!N28="","",('Porcentaje de Notas'!N28/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O28" s="23">
+      <c r="O28" s="19">
         <f>IF('Porcentaje de Notas'!O28="","",('Porcentaje de Notas'!O28/100)*$O$3)</f>
         <v>1.9</v>
       </c>
-      <c r="P28" s="23">
+      <c r="P28" s="19">
         <f>IF('Porcentaje de Notas'!P28="","",('Porcentaje de Notas'!P28/100)*$P$3)</f>
         <v>1.8</v>
       </c>
-      <c r="Q28" s="23">
+      <c r="Q28" s="19">
         <f>IF('Porcentaje de Notas'!Q28="","",('Porcentaje de Notas'!Q28/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R28" s="23">
+      <c r="R28" s="19">
         <f>IF('Porcentaje de Notas'!R28="","",('Porcentaje de Notas'!R28/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S28" s="23">
+      <c r="S28" s="19">
         <f>IF('Porcentaje de Notas'!S28="","",('Porcentaje de Notas'!S28/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T28" s="37">
+      <c r="T28" s="49">
         <f t="shared" si="0"/>
         <v>10.750000000000002</v>
       </c>
     </row>
     <row r="29" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C29" s="23">
+      <c r="C29" s="19">
         <v>25</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="19">
         <v>202432137</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="31">
         <f>IF('Porcentaje de Notas'!F29="","",('Porcentaje de Notas'!F29/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="19">
         <f>IF('Porcentaje de Notas'!G29="","",('Porcentaje de Notas'!G29/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="19">
         <f>IF('Porcentaje de Notas'!H29="","",('Porcentaje de Notas'!H29/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I29" s="36">
+      <c r="I29" s="32">
         <f>IF('Porcentaje de Notas'!I29="","",('Porcentaje de Notas'!I29/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="31">
         <f>IF('Porcentaje de Notas'!J29="","",('Porcentaje de Notas'!J29/100)*$J$3)</f>
         <v>0.5</v>
       </c>
-      <c r="K29" s="23">
+      <c r="K29" s="19">
         <f>IF('Porcentaje de Notas'!K29="","",('Porcentaje de Notas'!K29/100)*$K$3)</f>
         <v>0.5</v>
       </c>
-      <c r="L29" s="23">
+      <c r="L29" s="19">
         <f>IF('Porcentaje de Notas'!L29="","",('Porcentaje de Notas'!L29/100)*$L$3)</f>
         <v>0.5</v>
       </c>
-      <c r="M29" s="23">
+      <c r="M29" s="19">
         <f>IF('Porcentaje de Notas'!M29="","",('Porcentaje de Notas'!M29/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="23">
+      <c r="N29" s="19">
         <f>IF('Porcentaje de Notas'!N29="","",('Porcentaje de Notas'!N29/100)*$N$3)</f>
         <v>0.5</v>
       </c>
-      <c r="O29" s="23">
+      <c r="O29" s="19">
         <f>IF('Porcentaje de Notas'!O29="","",('Porcentaje de Notas'!O29/100)*$O$3)</f>
         <v>0.5</v>
       </c>
-      <c r="P29" s="23">
+      <c r="P29" s="19">
         <f>IF('Porcentaje de Notas'!P29="","",('Porcentaje de Notas'!P29/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q29" s="23">
+      <c r="Q29" s="19">
         <f>IF('Porcentaje de Notas'!Q29="","",('Porcentaje de Notas'!Q29/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R29" s="23">
+      <c r="R29" s="19">
         <f>IF('Porcentaje de Notas'!R29="","",('Porcentaje de Notas'!R29/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S29" s="23">
+      <c r="S29" s="19">
         <f>IF('Porcentaje de Notas'!S29="","",('Porcentaje de Notas'!S29/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T29" s="37">
+      <c r="T29" s="49">
         <f t="shared" si="0"/>
         <v>11.3</v>
       </c>
     </row>
     <row r="30" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C30" s="23">
+      <c r="C30" s="19">
         <v>26</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="19">
         <v>202530125</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="31">
         <f>IF('Porcentaje de Notas'!F30="","",('Porcentaje de Notas'!F30/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="19">
         <f>IF('Porcentaje de Notas'!G30="","",('Porcentaje de Notas'!G30/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="19">
         <f>IF('Porcentaje de Notas'!H30="","",('Porcentaje de Notas'!H30/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="32">
         <f>IF('Porcentaje de Notas'!I30="","",('Porcentaje de Notas'!I30/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="31">
         <f>IF('Porcentaje de Notas'!J30="","",('Porcentaje de Notas'!J30/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K30" s="23">
+      <c r="K30" s="19">
         <f>IF('Porcentaje de Notas'!K30="","",('Porcentaje de Notas'!K30/100)*$K$3)</f>
         <v>0.75</v>
       </c>
-      <c r="L30" s="23">
+      <c r="L30" s="19">
         <f>IF('Porcentaje de Notas'!L30="","",('Porcentaje de Notas'!L30/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M30" s="23">
+      <c r="M30" s="19">
         <f>IF('Porcentaje de Notas'!M30="","",('Porcentaje de Notas'!M30/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N30" s="23">
+      <c r="N30" s="19">
         <f>IF('Porcentaje de Notas'!N30="","",('Porcentaje de Notas'!N30/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O30" s="23">
+      <c r="O30" s="19">
         <f>IF('Porcentaje de Notas'!O30="","",('Porcentaje de Notas'!O30/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P30" s="23">
+      <c r="P30" s="19">
         <f>IF('Porcentaje de Notas'!P30="","",('Porcentaje de Notas'!P30/100)*$P$3)</f>
         <v>1.2</v>
       </c>
-      <c r="Q30" s="23">
+      <c r="Q30" s="19">
         <f>IF('Porcentaje de Notas'!Q30="","",('Porcentaje de Notas'!Q30/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R30" s="23">
+      <c r="R30" s="19">
         <f>IF('Porcentaje de Notas'!R30="","",('Porcentaje de Notas'!R30/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S30" s="23">
+      <c r="S30" s="19">
         <f>IF('Porcentaje de Notas'!S30="","",('Porcentaje de Notas'!S30/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T30" s="37">
+      <c r="T30" s="49">
         <f t="shared" si="0"/>
         <v>9.75</v>
       </c>
     </row>
     <row r="31" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C31" s="23">
+      <c r="C31" s="19">
         <v>27</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="19">
         <v>202530235</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="31">
         <f>IF('Porcentaje de Notas'!F31="","",('Porcentaje de Notas'!F31/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="19">
         <f>IF('Porcentaje de Notas'!G31="","",('Porcentaje de Notas'!G31/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="19">
         <f>IF('Porcentaje de Notas'!H31="","",('Porcentaje de Notas'!H31/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="32">
         <f>IF('Porcentaje de Notas'!I31="","",('Porcentaje de Notas'!I31/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="31">
         <f>IF('Porcentaje de Notas'!J31="","",('Porcentaje de Notas'!J31/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K31" s="23">
+      <c r="K31" s="19">
         <f>IF('Porcentaje de Notas'!K31="","",('Porcentaje de Notas'!K31/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L31" s="23">
+      <c r="L31" s="19">
         <f>IF('Porcentaje de Notas'!L31="","",('Porcentaje de Notas'!L31/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M31" s="23">
+      <c r="M31" s="19">
         <f>IF('Porcentaje de Notas'!M31="","",('Porcentaje de Notas'!M31/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N31" s="23">
+      <c r="N31" s="19">
         <f>IF('Porcentaje de Notas'!N31="","",('Porcentaje de Notas'!N31/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O31" s="23">
+      <c r="O31" s="19">
         <f>IF('Porcentaje de Notas'!O31="","",('Porcentaje de Notas'!O31/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P31" s="23">
+      <c r="P31" s="19">
         <f>IF('Porcentaje de Notas'!P31="","",('Porcentaje de Notas'!P31/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q31" s="23">
+      <c r="Q31" s="19">
         <f>IF('Porcentaje de Notas'!Q31="","",('Porcentaje de Notas'!Q31/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R31" s="23">
+      <c r="R31" s="19">
         <f>IF('Porcentaje de Notas'!R31="","",('Porcentaje de Notas'!R31/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S31" s="23">
+      <c r="S31" s="19">
         <f>IF('Porcentaje de Notas'!S31="","",('Porcentaje de Notas'!S31/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T31" s="37">
+      <c r="T31" s="49">
         <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
     </row>
     <row r="32" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C32" s="23">
+      <c r="C32" s="19">
         <v>28</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="19">
         <v>202530265</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="31">
         <f>IF('Porcentaje de Notas'!F32="","",('Porcentaje de Notas'!F32/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="19">
         <f>IF('Porcentaje de Notas'!G32="","",('Porcentaje de Notas'!G32/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="19">
         <f>IF('Porcentaje de Notas'!H32="","",('Porcentaje de Notas'!H32/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I32" s="36">
+      <c r="I32" s="32">
         <f>IF('Porcentaje de Notas'!I32="","",('Porcentaje de Notas'!I32/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="31">
         <f>IF('Porcentaje de Notas'!J32="","",('Porcentaje de Notas'!J32/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K32" s="23">
+      <c r="K32" s="19">
         <f>IF('Porcentaje de Notas'!K32="","",('Porcentaje de Notas'!K32/100)*$K$3)</f>
         <v>0.9</v>
       </c>
-      <c r="L32" s="23">
+      <c r="L32" s="19">
         <f>IF('Porcentaje de Notas'!L32="","",('Porcentaje de Notas'!L32/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M32" s="23">
+      <c r="M32" s="19">
         <f>IF('Porcentaje de Notas'!M32="","",('Porcentaje de Notas'!M32/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N32" s="23">
+      <c r="N32" s="19">
         <f>IF('Porcentaje de Notas'!N32="","",('Porcentaje de Notas'!N32/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O32" s="23">
+      <c r="O32" s="19">
         <f>IF('Porcentaje de Notas'!O32="","",('Porcentaje de Notas'!O32/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P32" s="23">
+      <c r="P32" s="19">
         <f>IF('Porcentaje de Notas'!P32="","",('Porcentaje de Notas'!P32/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q32" s="23">
+      <c r="Q32" s="19">
         <f>IF('Porcentaje de Notas'!Q32="","",('Porcentaje de Notas'!Q32/100)*$Q$3)</f>
         <v>0.9</v>
       </c>
-      <c r="R32" s="23">
+      <c r="R32" s="19">
         <f>IF('Porcentaje de Notas'!R32="","",('Porcentaje de Notas'!R32/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S32" s="23">
+      <c r="S32" s="19">
         <f>IF('Porcentaje de Notas'!S32="","",('Porcentaje de Notas'!S32/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T32" s="37">
+      <c r="T32" s="49">
         <f t="shared" si="0"/>
         <v>19.200000000000003</v>
       </c>
     </row>
     <row r="33" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C33" s="23">
+      <c r="C33" s="19">
         <v>29</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="19">
         <v>202530315</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="31">
         <f>IF('Porcentaje de Notas'!F33="","",('Porcentaje de Notas'!F33/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="19">
         <f>IF('Porcentaje de Notas'!G33="","",('Porcentaje de Notas'!G33/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="19">
         <f>IF('Porcentaje de Notas'!H33="","",('Porcentaje de Notas'!H33/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="32">
         <f>IF('Porcentaje de Notas'!I33="","",('Porcentaje de Notas'!I33/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="31">
         <f>IF('Porcentaje de Notas'!J33="","",('Porcentaje de Notas'!J33/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K33" s="23">
+      <c r="K33" s="19">
         <f>IF('Porcentaje de Notas'!K33="","",('Porcentaje de Notas'!K33/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L33" s="23">
+      <c r="L33" s="19">
         <f>IF('Porcentaje de Notas'!L33="","",('Porcentaje de Notas'!L33/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M33" s="23">
+      <c r="M33" s="19">
         <f>IF('Porcentaje de Notas'!M33="","",('Porcentaje de Notas'!M33/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N33" s="23">
+      <c r="N33" s="19">
         <f>IF('Porcentaje de Notas'!N33="","",('Porcentaje de Notas'!N33/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O33" s="23">
+      <c r="O33" s="19">
         <f>IF('Porcentaje de Notas'!O33="","",('Porcentaje de Notas'!O33/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P33" s="23">
+      <c r="P33" s="19">
         <f>IF('Porcentaje de Notas'!P33="","",('Porcentaje de Notas'!P33/100)*$P$3)</f>
         <v>1</v>
       </c>
-      <c r="Q33" s="23">
+      <c r="Q33" s="19">
         <f>IF('Porcentaje de Notas'!Q33="","",('Porcentaje de Notas'!Q33/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R33" s="23">
+      <c r="R33" s="19">
         <f>IF('Porcentaje de Notas'!R33="","",('Porcentaje de Notas'!R33/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S33" s="23">
+      <c r="S33" s="19">
         <f>IF('Porcentaje de Notas'!S33="","",('Porcentaje de Notas'!S33/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T33" s="37">
+      <c r="T33" s="49">
         <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
     </row>
     <row r="34" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C34" s="23">
+      <c r="C34" s="19">
         <v>30</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="19">
         <v>202530329</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="31">
         <f>IF('Porcentaje de Notas'!F34="","",('Porcentaje de Notas'!F34/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="19">
         <f>IF('Porcentaje de Notas'!G34="","",('Porcentaje de Notas'!G34/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="19">
         <f>IF('Porcentaje de Notas'!H34="","",('Porcentaje de Notas'!H34/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I34" s="36">
+      <c r="I34" s="32">
         <f>IF('Porcentaje de Notas'!I34="","",('Porcentaje de Notas'!I34/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="31">
         <f>IF('Porcentaje de Notas'!J34="","",('Porcentaje de Notas'!J34/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K34" s="23">
+      <c r="K34" s="19">
         <f>IF('Porcentaje de Notas'!K34="","",('Porcentaje de Notas'!K34/100)*$K$3)</f>
         <v>0.95</v>
       </c>
-      <c r="L34" s="23">
+      <c r="L34" s="19">
         <f>IF('Porcentaje de Notas'!L34="","",('Porcentaje de Notas'!L34/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M34" s="23">
+      <c r="M34" s="19">
         <f>IF('Porcentaje de Notas'!M34="","",('Porcentaje de Notas'!M34/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N34" s="23">
+      <c r="N34" s="19">
         <f>IF('Porcentaje de Notas'!N34="","",('Porcentaje de Notas'!N34/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O34" s="23">
+      <c r="O34" s="19">
         <f>IF('Porcentaje de Notas'!O34="","",('Porcentaje de Notas'!O34/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P34" s="23">
+      <c r="P34" s="19">
         <f>IF('Porcentaje de Notas'!P34="","",('Porcentaje de Notas'!P34/100)*$P$3)</f>
         <v>1.3</v>
       </c>
-      <c r="Q34" s="23">
+      <c r="Q34" s="19">
         <f>IF('Porcentaje de Notas'!Q34="","",('Porcentaje de Notas'!Q34/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R34" s="23">
+      <c r="R34" s="19">
         <f>IF('Porcentaje de Notas'!R34="","",('Porcentaje de Notas'!R34/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S34" s="23">
+      <c r="S34" s="19">
         <f>IF('Porcentaje de Notas'!S34="","",('Porcentaje de Notas'!S34/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T34" s="37">
+      <c r="T34" s="49">
         <f t="shared" si="0"/>
         <v>17.149999999999999</v>
       </c>
     </row>
     <row r="35" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C35" s="23">
+      <c r="C35" s="19">
         <v>31</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="19">
         <v>202530349</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="31">
         <f>IF('Porcentaje de Notas'!F35="","",('Porcentaje de Notas'!F35/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="19">
         <f>IF('Porcentaje de Notas'!G35="","",('Porcentaje de Notas'!G35/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="19">
         <f>IF('Porcentaje de Notas'!H35="","",('Porcentaje de Notas'!H35/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="32">
         <f>IF('Porcentaje de Notas'!I35="","",('Porcentaje de Notas'!I35/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="31">
         <f>IF('Porcentaje de Notas'!J35="","",('Porcentaje de Notas'!J35/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K35" s="23">
+      <c r="K35" s="19">
         <f>IF('Porcentaje de Notas'!K35="","",('Porcentaje de Notas'!K35/100)*$K$3)</f>
         <v>0.75</v>
       </c>
-      <c r="L35" s="23">
+      <c r="L35" s="19">
         <f>IF('Porcentaje de Notas'!L35="","",('Porcentaje de Notas'!L35/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M35" s="23">
+      <c r="M35" s="19">
         <f>IF('Porcentaje de Notas'!M35="","",('Porcentaje de Notas'!M35/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N35" s="23">
+      <c r="N35" s="19">
         <f>IF('Porcentaje de Notas'!N35="","",('Porcentaje de Notas'!N35/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O35" s="23">
+      <c r="O35" s="19">
         <f>IF('Porcentaje de Notas'!O35="","",('Porcentaje de Notas'!O35/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P35" s="23">
+      <c r="P35" s="19">
         <f>IF('Porcentaje de Notas'!P35="","",('Porcentaje de Notas'!P35/100)*$P$3)</f>
         <v>1.2</v>
       </c>
-      <c r="Q35" s="23">
+      <c r="Q35" s="19">
         <f>IF('Porcentaje de Notas'!Q35="","",('Porcentaje de Notas'!Q35/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R35" s="23">
+      <c r="R35" s="19">
         <f>IF('Porcentaje de Notas'!R35="","",('Porcentaje de Notas'!R35/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S35" s="23">
+      <c r="S35" s="19">
         <f>IF('Porcentaje de Notas'!S35="","",('Porcentaje de Notas'!S35/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T35" s="37">
+      <c r="T35" s="49">
         <f t="shared" si="0"/>
         <v>17.350000000000001</v>
       </c>
     </row>
     <row r="36" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C36" s="23">
+      <c r="C36" s="19">
         <v>32</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="19">
         <v>202530357</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="31">
         <f>IF('Porcentaje de Notas'!F36="","",('Porcentaje de Notas'!F36/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="19">
         <f>IF('Porcentaje de Notas'!G36="","",('Porcentaje de Notas'!G36/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="19">
         <f>IF('Porcentaje de Notas'!H36="","",('Porcentaje de Notas'!H36/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="32">
         <f>IF('Porcentaje de Notas'!I36="","",('Porcentaje de Notas'!I36/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="31">
         <f>IF('Porcentaje de Notas'!J36="","",('Porcentaje de Notas'!J36/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K36" s="23">
+      <c r="K36" s="19">
         <f>IF('Porcentaje de Notas'!K36="","",('Porcentaje de Notas'!K36/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L36" s="23">
+      <c r="L36" s="19">
         <f>IF('Porcentaje de Notas'!L36="","",('Porcentaje de Notas'!L36/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M36" s="23">
+      <c r="M36" s="19">
         <f>IF('Porcentaje de Notas'!M36="","",('Porcentaje de Notas'!M36/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N36" s="23">
+      <c r="N36" s="19">
         <f>IF('Porcentaje de Notas'!N36="","",('Porcentaje de Notas'!N36/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O36" s="23">
+      <c r="O36" s="19">
         <f>IF('Porcentaje de Notas'!O36="","",('Porcentaje de Notas'!O36/100)*$O$3)</f>
         <v>1.3</v>
       </c>
-      <c r="P36" s="23">
+      <c r="P36" s="19">
         <f>IF('Porcentaje de Notas'!P36="","",('Porcentaje de Notas'!P36/100)*$P$3)</f>
         <v>1.6</v>
       </c>
-      <c r="Q36" s="23">
+      <c r="Q36" s="19">
         <f>IF('Porcentaje de Notas'!Q36="","",('Porcentaje de Notas'!Q36/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R36" s="23">
+      <c r="R36" s="19">
         <f>IF('Porcentaje de Notas'!R36="","",('Porcentaje de Notas'!R36/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S36" s="23">
+      <c r="S36" s="19">
         <f>IF('Porcentaje de Notas'!S36="","",('Porcentaje de Notas'!S36/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T36" s="37">
+      <c r="T36" s="49">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
     <row r="37" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C37" s="23">
+      <c r="C37" s="19">
         <v>33</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="19">
         <v>202530381</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="F37" s="35">
+      <c r="F37" s="31">
         <f>IF('Porcentaje de Notas'!F37="","",('Porcentaje de Notas'!F37/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="19">
         <f>IF('Porcentaje de Notas'!G37="","",('Porcentaje de Notas'!G37/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="19">
         <f>IF('Porcentaje de Notas'!H37="","",('Porcentaje de Notas'!H37/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I37" s="36">
+      <c r="I37" s="32">
         <f>IF('Porcentaje de Notas'!I37="","",('Porcentaje de Notas'!I37/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="31">
         <f>IF('Porcentaje de Notas'!J37="","",('Porcentaje de Notas'!J37/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K37" s="23">
+      <c r="K37" s="19">
         <f>IF('Porcentaje de Notas'!K37="","",('Porcentaje de Notas'!K37/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L37" s="23">
+      <c r="L37" s="19">
         <f>IF('Porcentaje de Notas'!L37="","",('Porcentaje de Notas'!L37/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M37" s="23">
+      <c r="M37" s="19">
         <f>IF('Porcentaje de Notas'!M37="","",('Porcentaje de Notas'!M37/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N37" s="23">
+      <c r="N37" s="19">
         <f>IF('Porcentaje de Notas'!N37="","",('Porcentaje de Notas'!N37/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O37" s="23">
+      <c r="O37" s="19">
         <f>IF('Porcentaje de Notas'!O37="","",('Porcentaje de Notas'!O37/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P37" s="23">
+      <c r="P37" s="19">
         <f>IF('Porcentaje de Notas'!P37="","",('Porcentaje de Notas'!P37/100)*$P$3)</f>
         <v>0.9</v>
       </c>
-      <c r="Q37" s="23">
+      <c r="Q37" s="19">
         <f>IF('Porcentaje de Notas'!Q37="","",('Porcentaje de Notas'!Q37/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R37" s="23">
+      <c r="R37" s="19">
         <f>IF('Porcentaje de Notas'!R37="","",('Porcentaje de Notas'!R37/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S37" s="23">
+      <c r="S37" s="19">
         <f>IF('Porcentaje de Notas'!S37="","",('Porcentaje de Notas'!S37/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T37" s="37">
+      <c r="T37" s="49">
         <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
     </row>
     <row r="38" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C38" s="23">
+      <c r="C38" s="19">
         <v>34</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="19">
         <v>202530434</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="31">
         <f>IF('Porcentaje de Notas'!F38="","",('Porcentaje de Notas'!F38/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="19">
         <f>IF('Porcentaje de Notas'!G38="","",('Porcentaje de Notas'!G38/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="19">
         <f>IF('Porcentaje de Notas'!H38="","",('Porcentaje de Notas'!H38/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I38" s="36">
+      <c r="I38" s="32">
         <f>IF('Porcentaje de Notas'!I38="","",('Porcentaje de Notas'!I38/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="31">
         <f>IF('Porcentaje de Notas'!J38="","",('Porcentaje de Notas'!J38/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K38" s="23">
+      <c r="K38" s="19">
         <f>IF('Porcentaje de Notas'!K38="","",('Porcentaje de Notas'!K38/100)*$K$3)</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="L38" s="23">
+      <c r="L38" s="19">
         <f>IF('Porcentaje de Notas'!L38="","",('Porcentaje de Notas'!L38/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M38" s="23">
+      <c r="M38" s="19">
         <f>IF('Porcentaje de Notas'!M38="","",('Porcentaje de Notas'!M38/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N38" s="23">
+      <c r="N38" s="19">
         <f>IF('Porcentaje de Notas'!N38="","",('Porcentaje de Notas'!N38/100)*$N$3)</f>
         <v>1.8</v>
       </c>
-      <c r="O38" s="23">
+      <c r="O38" s="19">
         <f>IF('Porcentaje de Notas'!O38="","",('Porcentaje de Notas'!O38/100)*$O$3)</f>
         <v>1.5</v>
       </c>
-      <c r="P38" s="23">
+      <c r="P38" s="19">
         <f>IF('Porcentaje de Notas'!P38="","",('Porcentaje de Notas'!P38/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q38" s="23">
+      <c r="Q38" s="19">
         <f>IF('Porcentaje de Notas'!Q38="","",('Porcentaje de Notas'!Q38/100)*$Q$3)</f>
         <v>0.95</v>
       </c>
-      <c r="R38" s="23">
+      <c r="R38" s="19">
         <f>IF('Porcentaje de Notas'!R38="","",('Porcentaje de Notas'!R38/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S38" s="23">
+      <c r="S38" s="19">
         <f>IF('Porcentaje de Notas'!S38="","",('Porcentaje de Notas'!S38/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T38" s="37">
+      <c r="T38" s="49">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C39" s="23">
+      <c r="C39" s="19">
         <v>35</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="19">
         <v>202530446</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="31">
         <f>IF('Porcentaje de Notas'!F39="","",('Porcentaje de Notas'!F39/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="19">
         <f>IF('Porcentaje de Notas'!G39="","",('Porcentaje de Notas'!G39/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="19">
         <f>IF('Porcentaje de Notas'!H39="","",('Porcentaje de Notas'!H39/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I39" s="36">
+      <c r="I39" s="32">
         <f>IF('Porcentaje de Notas'!I39="","",('Porcentaje de Notas'!I39/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="31">
         <f>IF('Porcentaje de Notas'!J39="","",('Porcentaje de Notas'!J39/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K39" s="23">
+      <c r="K39" s="19">
         <f>IF('Porcentaje de Notas'!K39="","",('Porcentaje de Notas'!K39/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L39" s="23">
+      <c r="L39" s="19">
         <f>IF('Porcentaje de Notas'!L39="","",('Porcentaje de Notas'!L39/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M39" s="23">
+      <c r="M39" s="19">
         <f>IF('Porcentaje de Notas'!M39="","",('Porcentaje de Notas'!M39/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N39" s="23">
+      <c r="N39" s="19">
         <f>IF('Porcentaje de Notas'!N39="","",('Porcentaje de Notas'!N39/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O39" s="23">
+      <c r="O39" s="19">
         <f>IF('Porcentaje de Notas'!O39="","",('Porcentaje de Notas'!O39/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P39" s="23">
+      <c r="P39" s="19">
         <f>IF('Porcentaje de Notas'!P39="","",('Porcentaje de Notas'!P39/100)*$P$3)</f>
         <v>1.6</v>
       </c>
-      <c r="Q39" s="23">
+      <c r="Q39" s="19">
         <f>IF('Porcentaje de Notas'!Q39="","",('Porcentaje de Notas'!Q39/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R39" s="23">
+      <c r="R39" s="19">
         <f>IF('Porcentaje de Notas'!R39="","",('Porcentaje de Notas'!R39/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S39" s="23">
+      <c r="S39" s="19">
         <f>IF('Porcentaje de Notas'!S39="","",('Porcentaje de Notas'!S39/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T39" s="37">
+      <c r="T39" s="49">
         <f t="shared" si="0"/>
         <v>17.299999999999997</v>
       </c>
     </row>
     <row r="40" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C40" s="23">
+      <c r="C40" s="19">
         <v>36</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="19">
         <v>202530522</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="35">
+      <c r="F40" s="31">
         <f>IF('Porcentaje de Notas'!F40="","",('Porcentaje de Notas'!F40/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="19">
         <f>IF('Porcentaje de Notas'!G40="","",('Porcentaje de Notas'!G40/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="19">
         <f>IF('Porcentaje de Notas'!H40="","",('Porcentaje de Notas'!H40/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I40" s="36">
+      <c r="I40" s="32">
         <f>IF('Porcentaje de Notas'!I40="","",('Porcentaje de Notas'!I40/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J40" s="35">
+      <c r="J40" s="31">
         <f>IF('Porcentaje de Notas'!J40="","",('Porcentaje de Notas'!J40/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K40" s="23">
+      <c r="K40" s="19">
         <f>IF('Porcentaje de Notas'!K40="","",('Porcentaje de Notas'!K40/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L40" s="23">
+      <c r="L40" s="19">
         <f>IF('Porcentaje de Notas'!L40="","",('Porcentaje de Notas'!L40/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M40" s="23">
+      <c r="M40" s="19">
         <f>IF('Porcentaje de Notas'!M40="","",('Porcentaje de Notas'!M40/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N40" s="23">
+      <c r="N40" s="19">
         <f>IF('Porcentaje de Notas'!N40="","",('Porcentaje de Notas'!N40/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O40" s="23">
+      <c r="O40" s="19">
         <f>IF('Porcentaje de Notas'!O40="","",('Porcentaje de Notas'!O40/100)*$O$3)</f>
         <v>1.6</v>
       </c>
-      <c r="P40" s="23">
+      <c r="P40" s="19">
         <f>IF('Porcentaje de Notas'!P40="","",('Porcentaje de Notas'!P40/100)*$P$3)</f>
         <v>1.6</v>
       </c>
-      <c r="Q40" s="23">
+      <c r="Q40" s="19">
         <f>IF('Porcentaje de Notas'!Q40="","",('Porcentaje de Notas'!Q40/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R40" s="23">
+      <c r="R40" s="19">
         <f>IF('Porcentaje de Notas'!R40="","",('Porcentaje de Notas'!R40/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S40" s="23">
+      <c r="S40" s="19">
         <f>IF('Porcentaje de Notas'!S40="","",('Porcentaje de Notas'!S40/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T40" s="37">
+      <c r="T40" s="49">
         <f t="shared" si="0"/>
         <v>9.6999999999999993</v>
       </c>
     </row>
     <row r="41" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C41" s="23">
+      <c r="C41" s="19">
         <v>37</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="19">
         <v>202530613</v>
       </c>
-      <c r="E41" s="24" t="s">
+      <c r="E41" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="31">
         <f>IF('Porcentaje de Notas'!F41="","",('Porcentaje de Notas'!F41/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="19">
         <f>IF('Porcentaje de Notas'!G41="","",('Porcentaje de Notas'!G41/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="19">
         <f>IF('Porcentaje de Notas'!H41="","",('Porcentaje de Notas'!H41/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="36">
+      <c r="I41" s="32">
         <f>IF('Porcentaje de Notas'!I41="","",('Porcentaje de Notas'!I41/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="31">
         <f>IF('Porcentaje de Notas'!J41="","",('Porcentaje de Notas'!J41/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K41" s="23">
+      <c r="K41" s="19">
         <f>IF('Porcentaje de Notas'!K41="","",('Porcentaje de Notas'!K41/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="23">
+      <c r="L41" s="19">
         <f>IF('Porcentaje de Notas'!L41="","",('Porcentaje de Notas'!L41/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M41" s="23">
+      <c r="M41" s="19">
         <f>IF('Porcentaje de Notas'!M41="","",('Porcentaje de Notas'!M41/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N41" s="23">
+      <c r="N41" s="19">
         <f>IF('Porcentaje de Notas'!N41="","",('Porcentaje de Notas'!N41/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O41" s="23">
+      <c r="O41" s="19">
         <f>IF('Porcentaje de Notas'!O41="","",('Porcentaje de Notas'!O41/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P41" s="23">
+      <c r="P41" s="19">
         <f>IF('Porcentaje de Notas'!P41="","",('Porcentaje de Notas'!P41/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q41" s="23">
+      <c r="Q41" s="19">
         <f>IF('Porcentaje de Notas'!Q41="","",('Porcentaje de Notas'!Q41/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R41" s="23">
+      <c r="R41" s="19">
         <f>IF('Porcentaje de Notas'!R41="","",('Porcentaje de Notas'!R41/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S41" s="23">
+      <c r="S41" s="19">
         <f>IF('Porcentaje de Notas'!S41="","",('Porcentaje de Notas'!S41/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T41" s="37">
+      <c r="T41" s="49">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="42" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C42" s="23">
+      <c r="C42" s="19">
         <v>38</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="19">
         <v>202530621</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="35">
+      <c r="F42" s="31">
         <f>IF('Porcentaje de Notas'!F42="","",('Porcentaje de Notas'!F42/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="19">
         <f>IF('Porcentaje de Notas'!G42="","",('Porcentaje de Notas'!G42/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="19">
         <f>IF('Porcentaje de Notas'!H42="","",('Porcentaje de Notas'!H42/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I42" s="36">
+      <c r="I42" s="32">
         <f>IF('Porcentaje de Notas'!I42="","",('Porcentaje de Notas'!I42/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="31">
         <f>IF('Porcentaje de Notas'!J42="","",('Porcentaje de Notas'!J42/100)*$J$3)</f>
         <v>0.7</v>
       </c>
-      <c r="K42" s="23">
+      <c r="K42" s="19">
         <f>IF('Porcentaje de Notas'!K42="","",('Porcentaje de Notas'!K42/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L42" s="23">
+      <c r="L42" s="19">
         <f>IF('Porcentaje de Notas'!L42="","",('Porcentaje de Notas'!L42/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M42" s="23">
+      <c r="M42" s="19">
         <f>IF('Porcentaje de Notas'!M42="","",('Porcentaje de Notas'!M42/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N42" s="23">
+      <c r="N42" s="19">
         <f>IF('Porcentaje de Notas'!N42="","",('Porcentaje de Notas'!N42/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O42" s="23">
+      <c r="O42" s="19">
         <f>IF('Porcentaje de Notas'!O42="","",('Porcentaje de Notas'!O42/100)*$O$3)</f>
         <v>1.2</v>
       </c>
-      <c r="P42" s="23">
+      <c r="P42" s="19">
         <f>IF('Porcentaje de Notas'!P42="","",('Porcentaje de Notas'!P42/100)*$P$3)</f>
         <v>1.3</v>
       </c>
-      <c r="Q42" s="23">
+      <c r="Q42" s="19">
         <f>IF('Porcentaje de Notas'!Q42="","",('Porcentaje de Notas'!Q42/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R42" s="23">
+      <c r="R42" s="19">
         <f>IF('Porcentaje de Notas'!R42="","",('Porcentaje de Notas'!R42/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S42" s="23">
+      <c r="S42" s="19">
         <f>IF('Porcentaje de Notas'!S42="","",('Porcentaje de Notas'!S42/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T42" s="37">
+      <c r="T42" s="49">
         <f t="shared" si="0"/>
         <v>16.850000000000001</v>
       </c>
     </row>
     <row r="43" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C43" s="23">
+      <c r="C43" s="19">
         <v>39</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="19">
         <v>202530673</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E43" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="35">
+      <c r="F43" s="31">
         <f>IF('Porcentaje de Notas'!F43="","",('Porcentaje de Notas'!F43/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="19">
         <f>IF('Porcentaje de Notas'!G43="","",('Porcentaje de Notas'!G43/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="19">
         <f>IF('Porcentaje de Notas'!H43="","",('Porcentaje de Notas'!H43/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I43" s="36">
+      <c r="I43" s="32">
         <f>IF('Porcentaje de Notas'!I43="","",('Porcentaje de Notas'!I43/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="31">
         <f>IF('Porcentaje de Notas'!J43="","",('Porcentaje de Notas'!J43/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K43" s="23">
+      <c r="K43" s="19">
         <f>IF('Porcentaje de Notas'!K43="","",('Porcentaje de Notas'!K43/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L43" s="23">
+      <c r="L43" s="19">
         <f>IF('Porcentaje de Notas'!L43="","",('Porcentaje de Notas'!L43/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M43" s="23">
+      <c r="M43" s="19">
         <f>IF('Porcentaje de Notas'!M43="","",('Porcentaje de Notas'!M43/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N43" s="23">
+      <c r="N43" s="19">
         <f>IF('Porcentaje de Notas'!N43="","",('Porcentaje de Notas'!N43/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O43" s="23">
+      <c r="O43" s="19">
         <f>IF('Porcentaje de Notas'!O43="","",('Porcentaje de Notas'!O43/100)*$O$3)</f>
         <v>1.9</v>
       </c>
-      <c r="P43" s="23">
+      <c r="P43" s="19">
         <f>IF('Porcentaje de Notas'!P43="","",('Porcentaje de Notas'!P43/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q43" s="23">
+      <c r="Q43" s="19">
         <f>IF('Porcentaje de Notas'!Q43="","",('Porcentaje de Notas'!Q43/100)*$Q$3)</f>
         <v>0.5</v>
       </c>
-      <c r="R43" s="23">
+      <c r="R43" s="19">
         <f>IF('Porcentaje de Notas'!R43="","",('Porcentaje de Notas'!R43/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S43" s="23">
+      <c r="S43" s="19">
         <f>IF('Porcentaje de Notas'!S43="","",('Porcentaje de Notas'!S43/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T43" s="37">
+      <c r="T43" s="49">
         <f t="shared" si="0"/>
         <v>12.8</v>
       </c>
     </row>
     <row r="44" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C44" s="23">
+      <c r="C44" s="19">
         <v>40</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="19">
         <v>202530674</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="E44" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="31">
         <f>IF('Porcentaje de Notas'!F44="","",('Porcentaje de Notas'!F44/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="19">
         <f>IF('Porcentaje de Notas'!G44="","",('Porcentaje de Notas'!G44/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="23">
+      <c r="H44" s="19">
         <f>IF('Porcentaje de Notas'!H44="","",('Porcentaje de Notas'!H44/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I44" s="36">
+      <c r="I44" s="32">
         <f>IF('Porcentaje de Notas'!I44="","",('Porcentaje de Notas'!I44/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="31">
         <f>IF('Porcentaje de Notas'!J44="","",('Porcentaje de Notas'!J44/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K44" s="23">
+      <c r="K44" s="19">
         <f>IF('Porcentaje de Notas'!K44="","",('Porcentaje de Notas'!K44/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L44" s="23">
+      <c r="L44" s="19">
         <f>IF('Porcentaje de Notas'!L44="","",('Porcentaje de Notas'!L44/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M44" s="23">
+      <c r="M44" s="19">
         <f>IF('Porcentaje de Notas'!M44="","",('Porcentaje de Notas'!M44/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N44" s="23">
+      <c r="N44" s="19">
         <f>IF('Porcentaje de Notas'!N44="","",('Porcentaje de Notas'!N44/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O44" s="23">
+      <c r="O44" s="19">
         <f>IF('Porcentaje de Notas'!O44="","",('Porcentaje de Notas'!O44/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P44" s="23">
+      <c r="P44" s="19">
         <f>IF('Porcentaje de Notas'!P44="","",('Porcentaje de Notas'!P44/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q44" s="23">
+      <c r="Q44" s="19">
         <f>IF('Porcentaje de Notas'!Q44="","",('Porcentaje de Notas'!Q44/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R44" s="23">
+      <c r="R44" s="19">
         <f>IF('Porcentaje de Notas'!R44="","",('Porcentaje de Notas'!R44/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S44" s="23">
+      <c r="S44" s="19">
         <f>IF('Porcentaje de Notas'!S44="","",('Porcentaje de Notas'!S44/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T44" s="37">
+      <c r="T44" s="49">
         <f t="shared" si="0"/>
         <v>8.75</v>
       </c>
     </row>
     <row r="45" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C45" s="23">
+      <c r="C45" s="19">
         <v>41</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="19">
         <v>202530677</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="F45" s="35">
+      <c r="F45" s="31">
         <f>IF('Porcentaje de Notas'!F45="","",('Porcentaje de Notas'!F45/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="19">
         <f>IF('Porcentaje de Notas'!G45="","",('Porcentaje de Notas'!G45/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="19">
         <f>IF('Porcentaje de Notas'!H45="","",('Porcentaje de Notas'!H45/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I45" s="36">
+      <c r="I45" s="32">
         <f>IF('Porcentaje de Notas'!I45="","",('Porcentaje de Notas'!I45/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="31">
         <f>IF('Porcentaje de Notas'!J45="","",('Porcentaje de Notas'!J45/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K45" s="23">
+      <c r="K45" s="19">
         <f>IF('Porcentaje de Notas'!K45="","",('Porcentaje de Notas'!K45/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L45" s="23">
+      <c r="L45" s="19">
         <f>IF('Porcentaje de Notas'!L45="","",('Porcentaje de Notas'!L45/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M45" s="23">
+      <c r="M45" s="19">
         <f>IF('Porcentaje de Notas'!M45="","",('Porcentaje de Notas'!M45/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N45" s="23">
+      <c r="N45" s="19">
         <f>IF('Porcentaje de Notas'!N45="","",('Porcentaje de Notas'!N45/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O45" s="23">
+      <c r="O45" s="19">
         <f>IF('Porcentaje de Notas'!O45="","",('Porcentaje de Notas'!O45/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P45" s="23">
+      <c r="P45" s="19">
         <f>IF('Porcentaje de Notas'!P45="","",('Porcentaje de Notas'!P45/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q45" s="23">
+      <c r="Q45" s="19">
         <f>IF('Porcentaje de Notas'!Q45="","",('Porcentaje de Notas'!Q45/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R45" s="23">
+      <c r="R45" s="19">
         <f>IF('Porcentaje de Notas'!R45="","",('Porcentaje de Notas'!R45/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S45" s="23">
+      <c r="S45" s="19">
         <f>IF('Porcentaje de Notas'!S45="","",('Porcentaje de Notas'!S45/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T45" s="37">
+      <c r="T45" s="49">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="46" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C46" s="23">
+      <c r="C46" s="19">
         <v>42</v>
       </c>
-      <c r="D46" s="23">
+      <c r="D46" s="19">
         <v>202530728</v>
       </c>
-      <c r="E46" s="24" t="s">
+      <c r="E46" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="F46" s="35">
+      <c r="F46" s="31">
         <f>IF('Porcentaje de Notas'!F46="","",('Porcentaje de Notas'!F46/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="19">
         <f>IF('Porcentaje de Notas'!G46="","",('Porcentaje de Notas'!G46/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H46" s="23">
+      <c r="H46" s="19">
         <f>IF('Porcentaje de Notas'!H46="","",('Porcentaje de Notas'!H46/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I46" s="36">
+      <c r="I46" s="32">
         <f>IF('Porcentaje de Notas'!I46="","",('Porcentaje de Notas'!I46/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J46" s="35">
+      <c r="J46" s="31">
         <f>IF('Porcentaje de Notas'!J46="","",('Porcentaje de Notas'!J46/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K46" s="23">
+      <c r="K46" s="19">
         <f>IF('Porcentaje de Notas'!K46="","",('Porcentaje de Notas'!K46/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L46" s="23">
+      <c r="L46" s="19">
         <f>IF('Porcentaje de Notas'!L46="","",('Porcentaje de Notas'!L46/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M46" s="23">
+      <c r="M46" s="19">
         <f>IF('Porcentaje de Notas'!M46="","",('Porcentaje de Notas'!M46/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N46" s="23">
+      <c r="N46" s="19">
         <f>IF('Porcentaje de Notas'!N46="","",('Porcentaje de Notas'!N46/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O46" s="23">
+      <c r="O46" s="19">
         <f>IF('Porcentaje de Notas'!O46="","",('Porcentaje de Notas'!O46/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P46" s="23">
+      <c r="P46" s="19">
         <f>IF('Porcentaje de Notas'!P46="","",('Porcentaje de Notas'!P46/100)*$P$3)</f>
         <v>1</v>
       </c>
-      <c r="Q46" s="23">
+      <c r="Q46" s="19">
         <f>IF('Porcentaje de Notas'!Q46="","",('Porcentaje de Notas'!Q46/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R46" s="23">
+      <c r="R46" s="19">
         <f>IF('Porcentaje de Notas'!R46="","",('Porcentaje de Notas'!R46/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S46" s="23">
+      <c r="S46" s="19">
         <f>IF('Porcentaje de Notas'!S46="","",('Porcentaje de Notas'!S46/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T46" s="37">
+      <c r="T46" s="49">
         <f t="shared" si="0"/>
         <v>15.900000000000002</v>
       </c>
     </row>
     <row r="47" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C47" s="23">
+      <c r="C47" s="19">
         <v>43</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="19">
         <v>202530843</v>
       </c>
-      <c r="E47" s="24" t="s">
+      <c r="E47" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F47" s="35">
+      <c r="F47" s="31">
         <f>IF('Porcentaje de Notas'!F47="","",('Porcentaje de Notas'!F47/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="19">
         <f>IF('Porcentaje de Notas'!G47="","",('Porcentaje de Notas'!G47/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="19">
         <f>IF('Porcentaje de Notas'!H47="","",('Porcentaje de Notas'!H47/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I47" s="36">
+      <c r="I47" s="32">
         <f>IF('Porcentaje de Notas'!I47="","",('Porcentaje de Notas'!I47/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="31">
         <f>IF('Porcentaje de Notas'!J47="","",('Porcentaje de Notas'!J47/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K47" s="23">
+      <c r="K47" s="19">
         <f>IF('Porcentaje de Notas'!K47="","",('Porcentaje de Notas'!K47/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L47" s="23">
+      <c r="L47" s="19">
         <f>IF('Porcentaje de Notas'!L47="","",('Porcentaje de Notas'!L47/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M47" s="23">
+      <c r="M47" s="19">
         <f>IF('Porcentaje de Notas'!M47="","",('Porcentaje de Notas'!M47/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N47" s="23">
+      <c r="N47" s="19">
         <f>IF('Porcentaje de Notas'!N47="","",('Porcentaje de Notas'!N47/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O47" s="23">
+      <c r="O47" s="19">
         <f>IF('Porcentaje de Notas'!O47="","",('Porcentaje de Notas'!O47/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P47" s="23">
+      <c r="P47" s="19">
         <f>IF('Porcentaje de Notas'!P47="","",('Porcentaje de Notas'!P47/100)*$P$3)</f>
         <v>1.7</v>
       </c>
-      <c r="Q47" s="23">
+      <c r="Q47" s="19">
         <f>IF('Porcentaje de Notas'!Q47="","",('Porcentaje de Notas'!Q47/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R47" s="23">
+      <c r="R47" s="19">
         <f>IF('Porcentaje de Notas'!R47="","",('Porcentaje de Notas'!R47/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S47" s="23">
+      <c r="S47" s="19">
         <f>IF('Porcentaje de Notas'!S47="","",('Porcentaje de Notas'!S47/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T47" s="37">
+      <c r="T47" s="49">
         <f t="shared" si="0"/>
         <v>15.600000000000001</v>
       </c>
     </row>
     <row r="48" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C48" s="23">
+      <c r="C48" s="19">
         <v>44</v>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="19">
         <v>202530866</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F48" s="35">
+      <c r="F48" s="31">
         <f>IF('Porcentaje de Notas'!F48="","",('Porcentaje de Notas'!F48/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="19">
         <f>IF('Porcentaje de Notas'!G48="","",('Porcentaje de Notas'!G48/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="23">
+      <c r="H48" s="19">
         <f>IF('Porcentaje de Notas'!H48="","",('Porcentaje de Notas'!H48/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I48" s="36">
+      <c r="I48" s="32">
         <f>IF('Porcentaje de Notas'!I48="","",('Porcentaje de Notas'!I48/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="31">
         <f>IF('Porcentaje de Notas'!J48="","",('Porcentaje de Notas'!J48/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K48" s="23">
+      <c r="K48" s="19">
         <f>IF('Porcentaje de Notas'!K48="","",('Porcentaje de Notas'!K48/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L48" s="23">
+      <c r="L48" s="19">
         <f>IF('Porcentaje de Notas'!L48="","",('Porcentaje de Notas'!L48/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M48" s="23">
+      <c r="M48" s="19">
         <f>IF('Porcentaje de Notas'!M48="","",('Porcentaje de Notas'!M48/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N48" s="23">
+      <c r="N48" s="19">
         <f>IF('Porcentaje de Notas'!N48="","",('Porcentaje de Notas'!N48/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O48" s="23">
+      <c r="O48" s="19">
         <f>IF('Porcentaje de Notas'!O48="","",('Porcentaje de Notas'!O48/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P48" s="23">
+      <c r="P48" s="19">
         <f>IF('Porcentaje de Notas'!P48="","",('Porcentaje de Notas'!P48/100)*$P$3)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q48" s="23">
+      <c r="Q48" s="19">
         <f>IF('Porcentaje de Notas'!Q48="","",('Porcentaje de Notas'!Q48/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R48" s="23">
+      <c r="R48" s="19">
         <f>IF('Porcentaje de Notas'!R48="","",('Porcentaje de Notas'!R48/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S48" s="23">
+      <c r="S48" s="19">
         <f>IF('Porcentaje de Notas'!S48="","",('Porcentaje de Notas'!S48/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T48" s="37">
+      <c r="T48" s="49">
         <f t="shared" si="0"/>
         <v>17.149999999999999</v>
       </c>
     </row>
     <row r="49" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C49" s="23">
+      <c r="C49" s="19">
         <v>45</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="19">
         <v>202530917</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F49" s="38">
+      <c r="F49" s="31">
         <f>IF('Porcentaje de Notas'!F49="","",('Porcentaje de Notas'!F49/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G49" s="39">
+      <c r="G49" s="19">
         <f>IF('Porcentaje de Notas'!G49="","",('Porcentaje de Notas'!G49/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H49" s="23">
+      <c r="H49" s="19">
         <f>IF('Porcentaje de Notas'!H49="","",('Porcentaje de Notas'!H49/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I49" s="36">
+      <c r="I49" s="32">
         <f>IF('Porcentaje de Notas'!I49="","",('Porcentaje de Notas'!I49/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J49" s="35">
+      <c r="J49" s="31">
         <f>IF('Porcentaje de Notas'!J49="","",('Porcentaje de Notas'!J49/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K49" s="39">
+      <c r="K49" s="19">
         <f>IF('Porcentaje de Notas'!K49="","",('Porcentaje de Notas'!K49/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L49" s="23">
+      <c r="L49" s="19">
         <f>IF('Porcentaje de Notas'!L49="","",('Porcentaje de Notas'!L49/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M49" s="23">
+      <c r="M49" s="19">
         <f>IF('Porcentaje de Notas'!M49="","",('Porcentaje de Notas'!M49/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N49" s="23">
+      <c r="N49" s="19">
         <f>IF('Porcentaje de Notas'!N49="","",('Porcentaje de Notas'!N49/100)*$N$3)</f>
         <v>1.8</v>
       </c>
-      <c r="O49" s="23">
+      <c r="O49" s="19">
         <f>IF('Porcentaje de Notas'!O49="","",('Porcentaje de Notas'!O49/100)*$O$3)</f>
         <v>1.9</v>
       </c>
-      <c r="P49" s="23">
+      <c r="P49" s="19">
         <f>IF('Porcentaje de Notas'!P49="","",('Porcentaje de Notas'!P49/100)*$P$3)</f>
         <v>1.3</v>
       </c>
-      <c r="Q49" s="23">
+      <c r="Q49" s="19">
         <f>IF('Porcentaje de Notas'!Q49="","",('Porcentaje de Notas'!Q49/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R49" s="23">
+      <c r="R49" s="19">
         <f>IF('Porcentaje de Notas'!R49="","",('Porcentaje de Notas'!R49/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S49" s="23">
+      <c r="S49" s="19">
         <f>IF('Porcentaje de Notas'!S49="","",('Porcentaje de Notas'!S49/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T49" s="37">
+      <c r="T49" s="49">
         <f t="shared" si="0"/>
         <v>17.5</v>
       </c>
     </row>
     <row r="50" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C50" s="23">
+      <c r="C50" s="19">
         <v>46</v>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="19">
         <v>202531013</v>
       </c>
-      <c r="E50" s="24" t="s">
+      <c r="E50" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="35">
+      <c r="F50" s="31">
         <f>IF('Porcentaje de Notas'!F50="","",('Porcentaje de Notas'!F50/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G50" s="23">
+      <c r="G50" s="19">
         <f>IF('Porcentaje de Notas'!G50="","",('Porcentaje de Notas'!G50/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="19">
         <f>IF('Porcentaje de Notas'!H50="","",('Porcentaje de Notas'!H50/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I50" s="36">
+      <c r="I50" s="32">
         <f>IF('Porcentaje de Notas'!I50="","",('Porcentaje de Notas'!I50/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="31">
         <f>IF('Porcentaje de Notas'!J50="","",('Porcentaje de Notas'!J50/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K50" s="23">
+      <c r="K50" s="19">
         <f>IF('Porcentaje de Notas'!K50="","",('Porcentaje de Notas'!K50/100)*$K$3)</f>
         <v>0.75</v>
       </c>
-      <c r="L50" s="23">
+      <c r="L50" s="19">
         <f>IF('Porcentaje de Notas'!L50="","",('Porcentaje de Notas'!L50/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M50" s="23">
+      <c r="M50" s="19">
         <f>IF('Porcentaje de Notas'!M50="","",('Porcentaje de Notas'!M50/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N50" s="23">
+      <c r="N50" s="19">
         <f>IF('Porcentaje de Notas'!N50="","",('Porcentaje de Notas'!N50/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O50" s="23">
+      <c r="O50" s="19">
         <f>IF('Porcentaje de Notas'!O50="","",('Porcentaje de Notas'!O50/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P50" s="23">
+      <c r="P50" s="19">
         <f>IF('Porcentaje de Notas'!P50="","",('Porcentaje de Notas'!P50/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q50" s="23">
+      <c r="Q50" s="19">
         <f>IF('Porcentaje de Notas'!Q50="","",('Porcentaje de Notas'!Q50/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R50" s="23">
+      <c r="R50" s="19">
         <f>IF('Porcentaje de Notas'!R50="","",('Porcentaje de Notas'!R50/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S50" s="23">
+      <c r="S50" s="19">
         <f>IF('Porcentaje de Notas'!S50="","",('Porcentaje de Notas'!S50/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T50" s="37">
+      <c r="T50" s="49">
         <f t="shared" si="0"/>
         <v>18.399999999999999</v>
       </c>
     </row>
     <row r="51" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C51" s="23">
+      <c r="C51" s="19">
         <v>47</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="19">
         <v>202531019</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F51" s="35">
+      <c r="F51" s="31">
         <f>IF('Porcentaje de Notas'!F51="","",('Porcentaje de Notas'!F51/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G51" s="23">
+      <c r="G51" s="19">
         <f>IF('Porcentaje de Notas'!G51="","",('Porcentaje de Notas'!G51/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="19">
         <f>IF('Porcentaje de Notas'!H51="","",('Porcentaje de Notas'!H51/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I51" s="36">
+      <c r="I51" s="32">
         <f>IF('Porcentaje de Notas'!I51="","",('Porcentaje de Notas'!I51/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="31">
         <f>IF('Porcentaje de Notas'!J51="","",('Porcentaje de Notas'!J51/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K51" s="23">
+      <c r="K51" s="19">
         <f>IF('Porcentaje de Notas'!K51="","",('Porcentaje de Notas'!K51/100)*$K$3)</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="L51" s="23">
+      <c r="L51" s="19">
         <f>IF('Porcentaje de Notas'!L51="","",('Porcentaje de Notas'!L51/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M51" s="23">
+      <c r="M51" s="19">
         <f>IF('Porcentaje de Notas'!M51="","",('Porcentaje de Notas'!M51/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N51" s="23">
+      <c r="N51" s="19">
         <f>IF('Porcentaje de Notas'!N51="","",('Porcentaje de Notas'!N51/100)*$N$3)</f>
         <v>1.9</v>
       </c>
-      <c r="O51" s="23">
+      <c r="O51" s="19">
         <f>IF('Porcentaje de Notas'!O51="","",('Porcentaje de Notas'!O51/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P51" s="23">
+      <c r="P51" s="19">
         <f>IF('Porcentaje de Notas'!P51="","",('Porcentaje de Notas'!P51/100)*$P$3)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q51" s="23">
+      <c r="Q51" s="19">
         <f>IF('Porcentaje de Notas'!Q51="","",('Porcentaje de Notas'!Q51/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R51" s="23">
+      <c r="R51" s="19">
         <f>IF('Porcentaje de Notas'!R51="","",('Porcentaje de Notas'!R51/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S51" s="23">
+      <c r="S51" s="19">
         <f>IF('Porcentaje de Notas'!S51="","",('Porcentaje de Notas'!S51/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T51" s="37">
+      <c r="T51" s="49">
         <f t="shared" si="0"/>
         <v>15.5</v>
       </c>
     </row>
     <row r="52" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C52" s="23">
+      <c r="C52" s="19">
         <v>48</v>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="19">
         <v>202531089</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="F52" s="35">
+      <c r="F52" s="31">
         <f>IF('Porcentaje de Notas'!F52="","",('Porcentaje de Notas'!F52/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G52" s="23">
+      <c r="G52" s="19">
         <f>IF('Porcentaje de Notas'!G52="","",('Porcentaje de Notas'!G52/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H52" s="23">
+      <c r="H52" s="19">
         <f>IF('Porcentaje de Notas'!H52="","",('Porcentaje de Notas'!H52/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I52" s="36">
+      <c r="I52" s="32">
         <f>IF('Porcentaje de Notas'!I52="","",('Porcentaje de Notas'!I52/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J52" s="35">
+      <c r="J52" s="31">
         <f>IF('Porcentaje de Notas'!J52="","",('Porcentaje de Notas'!J52/100)*$J$3)</f>
         <v>0.7</v>
       </c>
-      <c r="K52" s="23">
+      <c r="K52" s="19">
         <f>IF('Porcentaje de Notas'!K52="","",('Porcentaje de Notas'!K52/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L52" s="23">
+      <c r="L52" s="19">
         <f>IF('Porcentaje de Notas'!L52="","",('Porcentaje de Notas'!L52/100)*$L$3)</f>
         <v>0.9</v>
       </c>
-      <c r="M52" s="23">
+      <c r="M52" s="19">
         <f>IF('Porcentaje de Notas'!M52="","",('Porcentaje de Notas'!M52/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N52" s="23">
+      <c r="N52" s="19">
         <f>IF('Porcentaje de Notas'!N52="","",('Porcentaje de Notas'!N52/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O52" s="23">
+      <c r="O52" s="19">
         <f>IF('Porcentaje de Notas'!O52="","",('Porcentaje de Notas'!O52/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P52" s="23">
+      <c r="P52" s="19">
         <f>IF('Porcentaje de Notas'!P52="","",('Porcentaje de Notas'!P52/100)*$P$3)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q52" s="23">
+      <c r="Q52" s="19">
         <f>IF('Porcentaje de Notas'!Q52="","",('Porcentaje de Notas'!Q52/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R52" s="23">
+      <c r="R52" s="19">
         <f>IF('Porcentaje de Notas'!R52="","",('Porcentaje de Notas'!R52/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S52" s="23">
+      <c r="S52" s="19">
         <f>IF('Porcentaje de Notas'!S52="","",('Porcentaje de Notas'!S52/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T52" s="37">
+      <c r="T52" s="49">
         <f t="shared" si="0"/>
         <v>16.850000000000001</v>
       </c>
     </row>
     <row r="53" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C53" s="23">
+      <c r="C53" s="19">
         <v>49</v>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="19">
         <v>202531127</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="35">
+      <c r="F53" s="31">
         <f>IF('Porcentaje de Notas'!F53="","",('Porcentaje de Notas'!F53/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G53" s="23">
+      <c r="G53" s="19">
         <f>IF('Porcentaje de Notas'!G53="","",('Porcentaje de Notas'!G53/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="19">
         <f>IF('Porcentaje de Notas'!H53="","",('Porcentaje de Notas'!H53/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I53" s="36">
+      <c r="I53" s="32">
         <f>IF('Porcentaje de Notas'!I53="","",('Porcentaje de Notas'!I53/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J53" s="35">
+      <c r="J53" s="31">
         <f>IF('Porcentaje de Notas'!J53="","",('Porcentaje de Notas'!J53/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K53" s="23">
+      <c r="K53" s="19">
         <f>IF('Porcentaje de Notas'!K53="","",('Porcentaje de Notas'!K53/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L53" s="23">
+      <c r="L53" s="19">
         <f>IF('Porcentaje de Notas'!L53="","",('Porcentaje de Notas'!L53/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="23">
+      <c r="M53" s="19">
         <f>IF('Porcentaje de Notas'!M53="","",('Porcentaje de Notas'!M53/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N53" s="23">
+      <c r="N53" s="19">
         <f>IF('Porcentaje de Notas'!N53="","",('Porcentaje de Notas'!N53/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O53" s="23">
+      <c r="O53" s="19">
         <f>IF('Porcentaje de Notas'!O53="","",('Porcentaje de Notas'!O53/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P53" s="23">
+      <c r="P53" s="19">
         <f>IF('Porcentaje de Notas'!P53="","",('Porcentaje de Notas'!P53/100)*$P$3)</f>
         <v>1.7</v>
       </c>
-      <c r="Q53" s="23">
+      <c r="Q53" s="19">
         <f>IF('Porcentaje de Notas'!Q53="","",('Porcentaje de Notas'!Q53/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R53" s="23">
+      <c r="R53" s="19">
         <f>IF('Porcentaje de Notas'!R53="","",('Porcentaje de Notas'!R53/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S53" s="23">
+      <c r="S53" s="19">
         <f>IF('Porcentaje de Notas'!S53="","",('Porcentaje de Notas'!S53/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T53" s="37">
+      <c r="T53" s="49">
         <f t="shared" si="0"/>
         <v>15.100000000000001</v>
       </c>
     </row>
     <row r="54" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C54" s="23">
+      <c r="C54" s="19">
         <v>50</v>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="19">
         <v>202531213</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F54" s="35">
+      <c r="F54" s="31">
         <f>IF('Porcentaje de Notas'!F54="","",('Porcentaje de Notas'!F54/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G54" s="23">
+      <c r="G54" s="19">
         <f>IF('Porcentaje de Notas'!G54="","",('Porcentaje de Notas'!G54/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H54" s="23">
+      <c r="H54" s="19">
         <f>IF('Porcentaje de Notas'!H54="","",('Porcentaje de Notas'!H54/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I54" s="36">
+      <c r="I54" s="32">
         <f>IF('Porcentaje de Notas'!I54="","",('Porcentaje de Notas'!I54/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J54" s="35">
+      <c r="J54" s="31">
         <f>IF('Porcentaje de Notas'!J54="","",('Porcentaje de Notas'!J54/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K54" s="23">
+      <c r="K54" s="19">
         <f>IF('Porcentaje de Notas'!K54="","",('Porcentaje de Notas'!K54/100)*$K$3)</f>
         <v>0.9</v>
       </c>
-      <c r="L54" s="23">
+      <c r="L54" s="19">
         <f>IF('Porcentaje de Notas'!L54="","",('Porcentaje de Notas'!L54/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M54" s="23">
+      <c r="M54" s="19">
         <f>IF('Porcentaje de Notas'!M54="","",('Porcentaje de Notas'!M54/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N54" s="23">
+      <c r="N54" s="19">
         <f>IF('Porcentaje de Notas'!N54="","",('Porcentaje de Notas'!N54/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O54" s="23">
+      <c r="O54" s="19">
         <f>IF('Porcentaje de Notas'!O54="","",('Porcentaje de Notas'!O54/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P54" s="23">
+      <c r="P54" s="19">
         <f>IF('Porcentaje de Notas'!P54="","",('Porcentaje de Notas'!P54/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q54" s="23">
+      <c r="Q54" s="19">
         <f>IF('Porcentaje de Notas'!Q54="","",('Porcentaje de Notas'!Q54/100)*$Q$3)</f>
         <v>0.9</v>
       </c>
-      <c r="R54" s="23">
+      <c r="R54" s="19">
         <f>IF('Porcentaje de Notas'!R54="","",('Porcentaje de Notas'!R54/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S54" s="23">
+      <c r="S54" s="19">
         <f>IF('Porcentaje de Notas'!S54="","",('Porcentaje de Notas'!S54/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T54" s="37">
+      <c r="T54" s="49">
         <f t="shared" si="0"/>
         <v>19.350000000000001</v>
       </c>
     </row>
     <row r="55" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C55" s="23">
+      <c r="C55" s="19">
         <v>51</v>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="19">
         <v>202531219</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="F55" s="35">
+      <c r="F55" s="31">
         <f>IF('Porcentaje de Notas'!F55="","",('Porcentaje de Notas'!F55/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G55" s="23">
+      <c r="G55" s="19">
         <f>IF('Porcentaje de Notas'!G55="","",('Porcentaje de Notas'!G55/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="19">
         <f>IF('Porcentaje de Notas'!H55="","",('Porcentaje de Notas'!H55/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I55" s="36">
+      <c r="I55" s="32">
         <f>IF('Porcentaje de Notas'!I55="","",('Porcentaje de Notas'!I55/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J55" s="35">
+      <c r="J55" s="31">
         <f>IF('Porcentaje de Notas'!J55="","",('Porcentaje de Notas'!J55/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K55" s="23">
+      <c r="K55" s="19">
         <f>IF('Porcentaje de Notas'!K55="","",('Porcentaje de Notas'!K55/100)*$K$3)</f>
         <v>0.9</v>
       </c>
-      <c r="L55" s="23">
+      <c r="L55" s="19">
         <f>IF('Porcentaje de Notas'!L55="","",('Porcentaje de Notas'!L55/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M55" s="23">
+      <c r="M55" s="19">
         <f>IF('Porcentaje de Notas'!M55="","",('Porcentaje de Notas'!M55/100)*$M$3)</f>
         <v>1.2000000000000002</v>
       </c>
-      <c r="N55" s="23">
+      <c r="N55" s="19">
         <f>IF('Porcentaje de Notas'!N55="","",('Porcentaje de Notas'!N55/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O55" s="23">
+      <c r="O55" s="19">
         <f>IF('Porcentaje de Notas'!O55="","",('Porcentaje de Notas'!O55/100)*$O$3)</f>
         <v>0.9</v>
       </c>
-      <c r="P55" s="23">
+      <c r="P55" s="19">
         <f>IF('Porcentaje de Notas'!P55="","",('Porcentaje de Notas'!P55/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="23">
+      <c r="Q55" s="19">
         <f>IF('Porcentaje de Notas'!Q55="","",('Porcentaje de Notas'!Q55/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R55" s="23">
+      <c r="R55" s="19">
         <f>IF('Porcentaje de Notas'!R55="","",('Porcentaje de Notas'!R55/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S55" s="23">
+      <c r="S55" s="19">
         <f>IF('Porcentaje de Notas'!S55="","",('Porcentaje de Notas'!S55/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T55" s="37">
+      <c r="T55" s="49">
         <f t="shared" si="0"/>
         <v>14.45</v>
       </c>
     </row>
     <row r="56" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C56" s="23">
+      <c r="C56" s="19">
         <v>52</v>
       </c>
-      <c r="D56" s="23">
+      <c r="D56" s="19">
         <v>202531289</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="F56" s="35">
+      <c r="F56" s="31">
         <f>IF('Porcentaje de Notas'!F56="","",('Porcentaje de Notas'!F56/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G56" s="23">
+      <c r="G56" s="19">
         <f>IF('Porcentaje de Notas'!G56="","",('Porcentaje de Notas'!G56/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="23">
+      <c r="H56" s="19">
         <f>IF('Porcentaje de Notas'!H56="","",('Porcentaje de Notas'!H56/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I56" s="36">
+      <c r="I56" s="32">
         <f>IF('Porcentaje de Notas'!I56="","",('Porcentaje de Notas'!I56/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J56" s="35">
+      <c r="J56" s="31">
         <f>IF('Porcentaje de Notas'!J56="","",('Porcentaje de Notas'!J56/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K56" s="23">
+      <c r="K56" s="19">
         <f>IF('Porcentaje de Notas'!K56="","",('Porcentaje de Notas'!K56/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L56" s="23">
+      <c r="L56" s="19">
         <f>IF('Porcentaje de Notas'!L56="","",('Porcentaje de Notas'!L56/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M56" s="23">
+      <c r="M56" s="19">
         <f>IF('Porcentaje de Notas'!M56="","",('Porcentaje de Notas'!M56/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N56" s="23">
+      <c r="N56" s="19">
         <f>IF('Porcentaje de Notas'!N56="","",('Porcentaje de Notas'!N56/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O56" s="23">
+      <c r="O56" s="19">
         <f>IF('Porcentaje de Notas'!O56="","",('Porcentaje de Notas'!O56/100)*$O$3)</f>
         <v>1.9</v>
       </c>
-      <c r="P56" s="23">
+      <c r="P56" s="19">
         <f>IF('Porcentaje de Notas'!P56="","",('Porcentaje de Notas'!P56/100)*$P$3)</f>
         <v>1.7</v>
       </c>
-      <c r="Q56" s="23">
+      <c r="Q56" s="19">
         <f>IF('Porcentaje de Notas'!Q56="","",('Porcentaje de Notas'!Q56/100)*$Q$3)</f>
         <v>0.95</v>
       </c>
-      <c r="R56" s="23">
+      <c r="R56" s="19">
         <f>IF('Porcentaje de Notas'!R56="","",('Porcentaje de Notas'!R56/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S56" s="23">
+      <c r="S56" s="19">
         <f>IF('Porcentaje de Notas'!S56="","",('Porcentaje de Notas'!S56/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T56" s="37">
+      <c r="T56" s="49">
         <f t="shared" si="0"/>
         <v>17.399999999999999</v>
       </c>
     </row>
     <row r="57" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C57" s="23">
+      <c r="C57" s="19">
         <v>53</v>
       </c>
-      <c r="D57" s="23">
+      <c r="D57" s="19">
         <v>202531319</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="31">
         <f>IF('Porcentaje de Notas'!F57="","",('Porcentaje de Notas'!F57/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G57" s="23">
+      <c r="G57" s="19">
         <f>IF('Porcentaje de Notas'!G57="","",('Porcentaje de Notas'!G57/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H57" s="23">
+      <c r="H57" s="19">
         <f>IF('Porcentaje de Notas'!H57="","",('Porcentaje de Notas'!H57/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I57" s="36">
+      <c r="I57" s="32">
         <f>IF('Porcentaje de Notas'!I57="","",('Porcentaje de Notas'!I57/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J57" s="35">
+      <c r="J57" s="31">
         <f>IF('Porcentaje de Notas'!J57="","",('Porcentaje de Notas'!J57/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K57" s="39">
+      <c r="K57" s="19">
         <f>IF('Porcentaje de Notas'!K57="","",('Porcentaje de Notas'!K57/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L57" s="23">
+      <c r="L57" s="19">
         <f>IF('Porcentaje de Notas'!L57="","",('Porcentaje de Notas'!L57/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M57" s="23">
+      <c r="M57" s="19">
         <f>IF('Porcentaje de Notas'!M57="","",('Porcentaje de Notas'!M57/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N57" s="23">
+      <c r="N57" s="19">
         <f>IF('Porcentaje de Notas'!N57="","",('Porcentaje de Notas'!N57/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O57" s="23">
+      <c r="O57" s="19">
         <f>IF('Porcentaje de Notas'!O57="","",('Porcentaje de Notas'!O57/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P57" s="23">
+      <c r="P57" s="19">
         <f>IF('Porcentaje de Notas'!P57="","",('Porcentaje de Notas'!P57/100)*$P$3)</f>
         <v>1</v>
       </c>
-      <c r="Q57" s="23">
+      <c r="Q57" s="19">
         <f>IF('Porcentaje de Notas'!Q57="","",('Porcentaje de Notas'!Q57/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R57" s="23">
+      <c r="R57" s="19">
         <f>IF('Porcentaje de Notas'!R57="","",('Porcentaje de Notas'!R57/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S57" s="23">
+      <c r="S57" s="19">
         <f>IF('Porcentaje de Notas'!S57="","",('Porcentaje de Notas'!S57/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T57" s="37">
+      <c r="T57" s="49">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="58" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C58" s="23">
+      <c r="C58" s="19">
         <v>54</v>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="19">
         <v>202531351</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F58" s="35">
+      <c r="F58" s="31">
         <f>IF('Porcentaje de Notas'!F58="","",('Porcentaje de Notas'!F58/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G58" s="23">
+      <c r="G58" s="19">
         <f>IF('Porcentaje de Notas'!G58="","",('Porcentaje de Notas'!G58/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H58" s="23">
+      <c r="H58" s="19">
         <f>IF('Porcentaje de Notas'!H58="","",('Porcentaje de Notas'!H58/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I58" s="36">
+      <c r="I58" s="32">
         <f>IF('Porcentaje de Notas'!I58="","",('Porcentaje de Notas'!I58/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J58" s="35">
+      <c r="J58" s="31">
         <f>IF('Porcentaje de Notas'!J58="","",('Porcentaje de Notas'!J58/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K58" s="23">
+      <c r="K58" s="19">
         <f>IF('Porcentaje de Notas'!K58="","",('Porcentaje de Notas'!K58/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L58" s="23">
+      <c r="L58" s="19">
         <f>IF('Porcentaje de Notas'!L58="","",('Porcentaje de Notas'!L58/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M58" s="23">
+      <c r="M58" s="19">
         <f>IF('Porcentaje de Notas'!M58="","",('Porcentaje de Notas'!M58/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N58" s="23">
+      <c r="N58" s="19">
         <f>IF('Porcentaje de Notas'!N58="","",('Porcentaje de Notas'!N58/100)*$N$3)</f>
         <v>1.6</v>
       </c>
-      <c r="O58" s="23">
+      <c r="O58" s="19">
         <f>IF('Porcentaje de Notas'!O58="","",('Porcentaje de Notas'!O58/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P58" s="23">
+      <c r="P58" s="19">
         <f>IF('Porcentaje de Notas'!P58="","",('Porcentaje de Notas'!P58/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q58" s="23">
+      <c r="Q58" s="19">
         <f>IF('Porcentaje de Notas'!Q58="","",('Porcentaje de Notas'!Q58/100)*$Q$3)</f>
         <v>0.9</v>
       </c>
-      <c r="R58" s="23">
+      <c r="R58" s="19">
         <f>IF('Porcentaje de Notas'!R58="","",('Porcentaje de Notas'!R58/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S58" s="23">
+      <c r="S58" s="19">
         <f>IF('Porcentaje de Notas'!S58="","",('Porcentaje de Notas'!S58/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T58" s="37">
+      <c r="T58" s="49">
         <f t="shared" si="0"/>
         <v>19.25</v>
       </c>
     </row>
     <row r="59" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C59" s="23">
+      <c r="C59" s="19">
         <v>55</v>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="19">
         <v>202531352</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="E59" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="F59" s="35">
+      <c r="F59" s="31">
         <f>IF('Porcentaje de Notas'!F59="","",('Porcentaje de Notas'!F59/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G59" s="23">
+      <c r="G59" s="19">
         <f>IF('Porcentaje de Notas'!G59="","",('Porcentaje de Notas'!G59/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="23">
+      <c r="H59" s="19">
         <f>IF('Porcentaje de Notas'!H59="","",('Porcentaje de Notas'!H59/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I59" s="36">
+      <c r="I59" s="32">
         <f>IF('Porcentaje de Notas'!I59="","",('Porcentaje de Notas'!I59/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J59" s="35">
+      <c r="J59" s="31">
         <f>IF('Porcentaje de Notas'!J59="","",('Porcentaje de Notas'!J59/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K59" s="23">
+      <c r="K59" s="19">
         <f>IF('Porcentaje de Notas'!K59="","",('Porcentaje de Notas'!K59/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L59" s="23">
+      <c r="L59" s="19">
         <f>IF('Porcentaje de Notas'!L59="","",('Porcentaje de Notas'!L59/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M59" s="23">
+      <c r="M59" s="19">
         <f>IF('Porcentaje de Notas'!M59="","",('Porcentaje de Notas'!M59/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N59" s="23">
+      <c r="N59" s="19">
         <f>IF('Porcentaje de Notas'!N59="","",('Porcentaje de Notas'!N59/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O59" s="23">
+      <c r="O59" s="19">
         <f>IF('Porcentaje de Notas'!O59="","",('Porcentaje de Notas'!O59/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P59" s="23">
+      <c r="P59" s="19">
         <f>IF('Porcentaje de Notas'!P59="","",('Porcentaje de Notas'!P59/100)*$P$3)</f>
         <v>1.5</v>
       </c>
-      <c r="Q59" s="23">
+      <c r="Q59" s="19">
         <f>IF('Porcentaje de Notas'!Q59="","",('Porcentaje de Notas'!Q59/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R59" s="23">
+      <c r="R59" s="19">
         <f>IF('Porcentaje de Notas'!R59="","",('Porcentaje de Notas'!R59/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S59" s="23">
+      <c r="S59" s="19">
         <f>IF('Porcentaje de Notas'!S59="","",('Porcentaje de Notas'!S59/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T59" s="37">
+      <c r="T59" s="49">
         <f t="shared" si="0"/>
         <v>14.700000000000001</v>
       </c>
     </row>
     <row r="60" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C60" s="23">
+      <c r="C60" s="19">
         <v>56</v>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="19">
         <v>202531384</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="31">
         <f>IF('Porcentaje de Notas'!F60="","",('Porcentaje de Notas'!F60/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="19">
         <f>IF('Porcentaje de Notas'!G60="","",('Porcentaje de Notas'!G60/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="19">
         <f>IF('Porcentaje de Notas'!H60="","",('Porcentaje de Notas'!H60/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I60" s="36">
+      <c r="I60" s="32">
         <f>IF('Porcentaje de Notas'!I60="","",('Porcentaje de Notas'!I60/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J60" s="35">
+      <c r="J60" s="31">
         <f>IF('Porcentaje de Notas'!J60="","",('Porcentaje de Notas'!J60/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K60" s="23">
+      <c r="K60" s="19">
         <f>IF('Porcentaje de Notas'!K60="","",('Porcentaje de Notas'!K60/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L60" s="23">
+      <c r="L60" s="19">
         <f>IF('Porcentaje de Notas'!L60="","",('Porcentaje de Notas'!L60/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M60" s="23">
+      <c r="M60" s="19">
         <f>IF('Porcentaje de Notas'!M60="","",('Porcentaje de Notas'!M60/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N60" s="23">
+      <c r="N60" s="19">
         <f>IF('Porcentaje de Notas'!N60="","",('Porcentaje de Notas'!N60/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O60" s="23">
+      <c r="O60" s="19">
         <f>IF('Porcentaje de Notas'!O60="","",('Porcentaje de Notas'!O60/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P60" s="23">
+      <c r="P60" s="19">
         <f>IF('Porcentaje de Notas'!P60="","",('Porcentaje de Notas'!P60/100)*$P$3)</f>
         <v>1.8</v>
       </c>
-      <c r="Q60" s="23">
+      <c r="Q60" s="19">
         <f>IF('Porcentaje de Notas'!Q60="","",('Porcentaje de Notas'!Q60/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R60" s="23">
+      <c r="R60" s="19">
         <f>IF('Porcentaje de Notas'!R60="","",('Porcentaje de Notas'!R60/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S60" s="23">
+      <c r="S60" s="19">
         <f>IF('Porcentaje de Notas'!S60="","",('Porcentaje de Notas'!S60/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T60" s="37">
+      <c r="T60" s="49">
         <f t="shared" si="0"/>
         <v>18.700000000000003</v>
       </c>
     </row>
     <row r="61" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C61" s="23">
+      <c r="C61" s="19">
         <v>57</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="19">
         <v>202531399</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="35">
+      <c r="F61" s="31">
         <f>IF('Porcentaje de Notas'!F61="","",('Porcentaje de Notas'!F61/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G61" s="23">
+      <c r="G61" s="19">
         <f>IF('Porcentaje de Notas'!G61="","",('Porcentaje de Notas'!G61/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="19">
         <f>IF('Porcentaje de Notas'!H61="","",('Porcentaje de Notas'!H61/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I61" s="36">
+      <c r="I61" s="32">
         <f>IF('Porcentaje de Notas'!I61="","",('Porcentaje de Notas'!I61/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J61" s="35">
+      <c r="J61" s="31">
         <f>IF('Porcentaje de Notas'!J61="","",('Porcentaje de Notas'!J61/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K61" s="23">
+      <c r="K61" s="19">
         <f>IF('Porcentaje de Notas'!K61="","",('Porcentaje de Notas'!K61/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L61" s="23">
+      <c r="L61" s="19">
         <f>IF('Porcentaje de Notas'!L61="","",('Porcentaje de Notas'!L61/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M61" s="23">
+      <c r="M61" s="19">
         <f>IF('Porcentaje de Notas'!M61="","",('Porcentaje de Notas'!M61/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N61" s="23">
+      <c r="N61" s="19">
         <f>IF('Porcentaje de Notas'!N61="","",('Porcentaje de Notas'!N61/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O61" s="23">
+      <c r="O61" s="19">
         <f>IF('Porcentaje de Notas'!O61="","",('Porcentaje de Notas'!O61/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P61" s="23">
+      <c r="P61" s="19">
         <f>IF('Porcentaje de Notas'!P61="","",('Porcentaje de Notas'!P61/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q61" s="23">
+      <c r="Q61" s="19">
         <f>IF('Porcentaje de Notas'!Q61="","",('Porcentaje de Notas'!Q61/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R61" s="23">
+      <c r="R61" s="19">
         <f>IF('Porcentaje de Notas'!R61="","",('Porcentaje de Notas'!R61/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S61" s="23">
+      <c r="S61" s="19">
         <f>IF('Porcentaje de Notas'!S61="","",('Porcentaje de Notas'!S61/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T61" s="37">
+      <c r="T61" s="49">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
     </row>
     <row r="62" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C62" s="23">
+      <c r="C62" s="19">
         <v>58</v>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="19">
         <v>202531441</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F62" s="35">
+      <c r="F62" s="31">
         <f>IF('Porcentaje de Notas'!F62="","",('Porcentaje de Notas'!F62/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G62" s="23">
+      <c r="G62" s="19">
         <f>IF('Porcentaje de Notas'!G62="","",('Porcentaje de Notas'!G62/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="19">
         <f>IF('Porcentaje de Notas'!H62="","",('Porcentaje de Notas'!H62/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I62" s="36">
+      <c r="I62" s="32">
         <f>IF('Porcentaje de Notas'!I62="","",('Porcentaje de Notas'!I62/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J62" s="35">
+      <c r="J62" s="31">
         <f>IF('Porcentaje de Notas'!J62="","",('Porcentaje de Notas'!J62/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K62" s="23">
+      <c r="K62" s="19">
         <f>IF('Porcentaje de Notas'!K62="","",('Porcentaje de Notas'!K62/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L62" s="23">
+      <c r="L62" s="19">
         <f>IF('Porcentaje de Notas'!L62="","",('Porcentaje de Notas'!L62/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M62" s="23">
+      <c r="M62" s="19">
         <f>IF('Porcentaje de Notas'!M62="","",('Porcentaje de Notas'!M62/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N62" s="23">
+      <c r="N62" s="19">
         <f>IF('Porcentaje de Notas'!N62="","",('Porcentaje de Notas'!N62/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O62" s="23">
+      <c r="O62" s="19">
         <f>IF('Porcentaje de Notas'!O62="","",('Porcentaje de Notas'!O62/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P62" s="23">
+      <c r="P62" s="19">
         <f>IF('Porcentaje de Notas'!P62="","",('Porcentaje de Notas'!P62/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q62" s="23">
+      <c r="Q62" s="19">
         <f>IF('Porcentaje de Notas'!Q62="","",('Porcentaje de Notas'!Q62/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R62" s="23">
+      <c r="R62" s="19">
         <f>IF('Porcentaje de Notas'!R62="","",('Porcentaje de Notas'!R62/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S62" s="23">
+      <c r="S62" s="19">
         <f>IF('Porcentaje de Notas'!S62="","",('Porcentaje de Notas'!S62/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T62" s="37">
+      <c r="T62" s="49">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C63" s="23">
+      <c r="C63" s="19">
         <v>59</v>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="19">
         <v>202531444</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F63" s="35">
+      <c r="F63" s="31">
         <f>IF('Porcentaje de Notas'!F63="","",('Porcentaje de Notas'!F63/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G63" s="23">
+      <c r="G63" s="19">
         <f>IF('Porcentaje de Notas'!G63="","",('Porcentaje de Notas'!G63/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="19">
         <f>IF('Porcentaje de Notas'!H63="","",('Porcentaje de Notas'!H63/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I63" s="36">
+      <c r="I63" s="32">
         <f>IF('Porcentaje de Notas'!I63="","",('Porcentaje de Notas'!I63/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J63" s="35">
+      <c r="J63" s="31">
         <f>IF('Porcentaje de Notas'!J63="","",('Porcentaje de Notas'!J63/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K63" s="23">
+      <c r="K63" s="19">
         <f>IF('Porcentaje de Notas'!K63="","",('Porcentaje de Notas'!K63/100)*$K$3)</f>
         <v>0.95</v>
       </c>
-      <c r="L63" s="23">
+      <c r="L63" s="19">
         <f>IF('Porcentaje de Notas'!L63="","",('Porcentaje de Notas'!L63/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M63" s="23">
+      <c r="M63" s="19">
         <f>IF('Porcentaje de Notas'!M63="","",('Porcentaje de Notas'!M63/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N63" s="23">
+      <c r="N63" s="19">
         <f>IF('Porcentaje de Notas'!N63="","",('Porcentaje de Notas'!N63/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O63" s="23">
+      <c r="O63" s="19">
         <f>IF('Porcentaje de Notas'!O63="","",('Porcentaje de Notas'!O63/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P63" s="23">
+      <c r="P63" s="19">
         <f>IF('Porcentaje de Notas'!P63="","",('Porcentaje de Notas'!P63/100)*$P$3)</f>
         <v>1.3</v>
       </c>
-      <c r="Q63" s="23">
+      <c r="Q63" s="19">
         <f>IF('Porcentaje de Notas'!Q63="","",('Porcentaje de Notas'!Q63/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R63" s="23">
+      <c r="R63" s="19">
         <f>IF('Porcentaje de Notas'!R63="","",('Porcentaje de Notas'!R63/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S63" s="23">
+      <c r="S63" s="19">
         <f>IF('Porcentaje de Notas'!S63="","",('Porcentaje de Notas'!S63/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T63" s="37">
+      <c r="T63" s="49">
         <f t="shared" si="0"/>
         <v>15.700000000000001</v>
       </c>
     </row>
     <row r="64" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C64" s="23">
+      <c r="C64" s="19">
         <v>60</v>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="19">
         <v>202531566</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F64" s="35">
+      <c r="F64" s="31">
         <f>IF('Porcentaje de Notas'!F64="","",('Porcentaje de Notas'!F64/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G64" s="23">
+      <c r="G64" s="19">
         <f>IF('Porcentaje de Notas'!G64="","",('Porcentaje de Notas'!G64/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="19">
         <f>IF('Porcentaje de Notas'!H64="","",('Porcentaje de Notas'!H64/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I64" s="36">
+      <c r="I64" s="32">
         <f>IF('Porcentaje de Notas'!I64="","",('Porcentaje de Notas'!I64/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J64" s="35">
+      <c r="J64" s="31">
         <f>IF('Porcentaje de Notas'!J64="","",('Porcentaje de Notas'!J64/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K64" s="23">
+      <c r="K64" s="19">
         <f>IF('Porcentaje de Notas'!K64="","",('Porcentaje de Notas'!K64/100)*$K$3)</f>
         <v>0.85</v>
       </c>
-      <c r="L64" s="23">
+      <c r="L64" s="19">
         <f>IF('Porcentaje de Notas'!L64="","",('Porcentaje de Notas'!L64/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M64" s="23">
+      <c r="M64" s="19">
         <f>IF('Porcentaje de Notas'!M64="","",('Porcentaje de Notas'!M64/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N64" s="23">
+      <c r="N64" s="19">
         <f>IF('Porcentaje de Notas'!N64="","",('Porcentaje de Notas'!N64/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O64" s="23">
+      <c r="O64" s="19">
         <f>IF('Porcentaje de Notas'!O64="","",('Porcentaje de Notas'!O64/100)*$O$3)</f>
         <v>1.5</v>
       </c>
-      <c r="P64" s="23">
+      <c r="P64" s="19">
         <f>IF('Porcentaje de Notas'!P64="","",('Porcentaje de Notas'!P64/100)*$P$3)</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q64" s="23">
+      <c r="Q64" s="19">
         <f>IF('Porcentaje de Notas'!Q64="","",('Porcentaje de Notas'!Q64/100)*$Q$3)</f>
         <v>0.95</v>
       </c>
-      <c r="R64" s="23">
+      <c r="R64" s="19">
         <f>IF('Porcentaje de Notas'!R64="","",('Porcentaje de Notas'!R64/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S64" s="23">
+      <c r="S64" s="19">
         <f>IF('Porcentaje de Notas'!S64="","",('Porcentaje de Notas'!S64/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T64" s="37">
+      <c r="T64" s="49">
         <f t="shared" si="0"/>
         <v>17.25</v>
       </c>
     </row>
     <row r="65" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C65" s="23">
+      <c r="C65" s="19">
         <v>61</v>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="19">
         <v>202531611</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F65" s="35">
+      <c r="F65" s="31">
         <f>IF('Porcentaje de Notas'!F65="","",('Porcentaje de Notas'!F65/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G65" s="23">
+      <c r="G65" s="19">
         <f>IF('Porcentaje de Notas'!G65="","",('Porcentaje de Notas'!G65/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="19">
         <f>IF('Porcentaje de Notas'!H65="","",('Porcentaje de Notas'!H65/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I65" s="36">
+      <c r="I65" s="32">
         <f>IF('Porcentaje de Notas'!I65="","",('Porcentaje de Notas'!I65/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J65" s="35">
+      <c r="J65" s="31">
         <f>IF('Porcentaje de Notas'!J65="","",('Porcentaje de Notas'!J65/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K65" s="23">
+      <c r="K65" s="19">
         <f>IF('Porcentaje de Notas'!K65="","",('Porcentaje de Notas'!K65/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L65" s="23">
+      <c r="L65" s="19">
         <f>IF('Porcentaje de Notas'!L65="","",('Porcentaje de Notas'!L65/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M65" s="23">
+      <c r="M65" s="19">
         <f>IF('Porcentaje de Notas'!M65="","",('Porcentaje de Notas'!M65/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N65" s="23">
+      <c r="N65" s="19">
         <f>IF('Porcentaje de Notas'!N65="","",('Porcentaje de Notas'!N65/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O65" s="23">
+      <c r="O65" s="19">
         <f>IF('Porcentaje de Notas'!O65="","",('Porcentaje de Notas'!O65/100)*$O$3)</f>
         <v>0.9</v>
       </c>
-      <c r="P65" s="23">
+      <c r="P65" s="19">
         <f>IF('Porcentaje de Notas'!P65="","",('Porcentaje de Notas'!P65/100)*$P$3)</f>
         <v>1.5</v>
       </c>
-      <c r="Q65" s="23">
+      <c r="Q65" s="19">
         <f>IF('Porcentaje de Notas'!Q65="","",('Porcentaje de Notas'!Q65/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R65" s="23">
+      <c r="R65" s="19">
         <f>IF('Porcentaje de Notas'!R65="","",('Porcentaje de Notas'!R65/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S65" s="23">
+      <c r="S65" s="19">
         <f>IF('Porcentaje de Notas'!S65="","",('Porcentaje de Notas'!S65/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T65" s="37">
+      <c r="T65" s="49">
         <f t="shared" si="0"/>
         <v>14.05</v>
       </c>
     </row>
     <row r="66" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C66" s="23">
+      <c r="C66" s="19">
         <v>62</v>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="19">
         <v>202531645</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F66" s="35">
+      <c r="F66" s="31">
         <f>IF('Porcentaje de Notas'!F66="","",('Porcentaje de Notas'!F66/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G66" s="23">
+      <c r="G66" s="19">
         <f>IF('Porcentaje de Notas'!G66="","",('Porcentaje de Notas'!G66/100)*$G$3)</f>
         <v>0.5</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="19">
         <f>IF('Porcentaje de Notas'!H66="","",('Porcentaje de Notas'!H66/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I66" s="36">
+      <c r="I66" s="32">
         <f>IF('Porcentaje de Notas'!I66="","",('Porcentaje de Notas'!I66/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J66" s="35">
+      <c r="J66" s="31">
         <f>IF('Porcentaje de Notas'!J66="","",('Porcentaje de Notas'!J66/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K66" s="23">
+      <c r="K66" s="19">
         <f>IF('Porcentaje de Notas'!K66="","",('Porcentaje de Notas'!K66/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L66" s="23">
+      <c r="L66" s="19">
         <f>IF('Porcentaje de Notas'!L66="","",('Porcentaje de Notas'!L66/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M66" s="23">
+      <c r="M66" s="19">
         <f>IF('Porcentaje de Notas'!M66="","",('Porcentaje de Notas'!M66/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N66" s="23">
+      <c r="N66" s="19">
         <f>IF('Porcentaje de Notas'!N66="","",('Porcentaje de Notas'!N66/100)*$N$3)</f>
-        <v>0</v>
-      </c>
-      <c r="O66" s="23">
+        <v>0.8</v>
+      </c>
+      <c r="O66" s="19">
         <f>IF('Porcentaje de Notas'!O66="","",('Porcentaje de Notas'!O66/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P66" s="23">
+      <c r="P66" s="19">
         <f>IF('Porcentaje de Notas'!P66="","",('Porcentaje de Notas'!P66/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q66" s="23">
+      <c r="Q66" s="19">
         <f>IF('Porcentaje de Notas'!Q66="","",('Porcentaje de Notas'!Q66/100)*$Q$3)</f>
         <v>0.9</v>
       </c>
-      <c r="R66" s="23">
+      <c r="R66" s="19">
         <f>IF('Porcentaje de Notas'!R66="","",('Porcentaje de Notas'!R66/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S66" s="23">
+      <c r="S66" s="19">
         <f>IF('Porcentaje de Notas'!S66="","",('Porcentaje de Notas'!S66/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T66" s="37">
+      <c r="T66" s="49">
         <f t="shared" si="0"/>
-        <v>16.149999999999999</v>
+        <v>16.950000000000003</v>
       </c>
     </row>
     <row r="67" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C67" s="23">
+      <c r="C67" s="19">
         <v>63</v>
       </c>
-      <c r="D67" s="23">
+      <c r="D67" s="19">
         <v>202531663</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F67" s="35">
+      <c r="F67" s="31">
         <f>IF('Porcentaje de Notas'!F67="","",('Porcentaje de Notas'!F67/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G67" s="23">
+      <c r="G67" s="19">
         <f>IF('Porcentaje de Notas'!G67="","",('Porcentaje de Notas'!G67/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="19">
         <f>IF('Porcentaje de Notas'!H67="","",('Porcentaje de Notas'!H67/100)*$H$3)</f>
         <v>0</v>
       </c>
-      <c r="I67" s="36">
+      <c r="I67" s="32">
         <f>IF('Porcentaje de Notas'!I67="","",('Porcentaje de Notas'!I67/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J67" s="35">
+      <c r="J67" s="31">
         <f>IF('Porcentaje de Notas'!J67="","",('Porcentaje de Notas'!J67/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K67" s="23">
+      <c r="K67" s="19">
         <f>IF('Porcentaje de Notas'!K67="","",('Porcentaje de Notas'!K67/100)*$K$3)</f>
         <v>0</v>
       </c>
-      <c r="L67" s="23">
+      <c r="L67" s="19">
         <f>IF('Porcentaje de Notas'!L67="","",('Porcentaje de Notas'!L67/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M67" s="23">
+      <c r="M67" s="19">
         <f>IF('Porcentaje de Notas'!M67="","",('Porcentaje de Notas'!M67/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N67" s="23">
+      <c r="N67" s="19">
         <f>IF('Porcentaje de Notas'!N67="","",('Porcentaje de Notas'!N67/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O67" s="23">
+      <c r="O67" s="19">
         <f>IF('Porcentaje de Notas'!O67="","",('Porcentaje de Notas'!O67/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P67" s="23">
+      <c r="P67" s="19">
         <f>IF('Porcentaje de Notas'!P67="","",('Porcentaje de Notas'!P67/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q67" s="23">
+      <c r="Q67" s="19">
         <f>IF('Porcentaje de Notas'!Q67="","",('Porcentaje de Notas'!Q67/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R67" s="23">
+      <c r="R67" s="19">
         <f>IF('Porcentaje de Notas'!R67="","",('Porcentaje de Notas'!R67/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S67" s="23">
+      <c r="S67" s="19">
         <f>IF('Porcentaje de Notas'!S67="","",('Porcentaje de Notas'!S67/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T67" s="37">
+      <c r="T67" s="49">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="68" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C68" s="23">
+      <c r="C68" s="19">
         <v>64</v>
       </c>
-      <c r="D68" s="23">
+      <c r="D68" s="19">
         <v>202531724</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F68" s="35">
+      <c r="F68" s="31">
         <f>IF('Porcentaje de Notas'!F68="","",('Porcentaje de Notas'!F68/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="19">
         <f>IF('Porcentaje de Notas'!G68="","",('Porcentaje de Notas'!G68/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="19">
         <f>IF('Porcentaje de Notas'!H68="","",('Porcentaje de Notas'!H68/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I68" s="36">
+      <c r="I68" s="32">
         <f>IF('Porcentaje de Notas'!I68="","",('Porcentaje de Notas'!I68/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="31">
         <f>IF('Porcentaje de Notas'!J68="","",('Porcentaje de Notas'!J68/100)*$J$3)</f>
         <v>0.4</v>
       </c>
-      <c r="K68" s="23">
+      <c r="K68" s="19">
         <f>IF('Porcentaje de Notas'!K68="","",('Porcentaje de Notas'!K68/100)*$K$3)</f>
         <v>0.85</v>
       </c>
-      <c r="L68" s="23">
+      <c r="L68" s="19">
         <f>IF('Porcentaje de Notas'!L68="","",('Porcentaje de Notas'!L68/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M68" s="23">
+      <c r="M68" s="19">
         <f>IF('Porcentaje de Notas'!M68="","",('Porcentaje de Notas'!M68/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N68" s="23">
+      <c r="N68" s="19">
         <f>IF('Porcentaje de Notas'!N68="","",('Porcentaje de Notas'!N68/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O68" s="23">
+      <c r="O68" s="19">
         <f>IF('Porcentaje de Notas'!O68="","",('Porcentaje de Notas'!O68/100)*$O$3)</f>
         <v>1.5</v>
       </c>
-      <c r="P68" s="23">
+      <c r="P68" s="19">
         <f>IF('Porcentaje de Notas'!P68="","",('Porcentaje de Notas'!P68/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q68" s="23">
+      <c r="Q68" s="19">
         <f>IF('Porcentaje de Notas'!Q68="","",('Porcentaje de Notas'!Q68/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R68" s="23">
+      <c r="R68" s="19">
         <f>IF('Porcentaje de Notas'!R68="","",('Porcentaje de Notas'!R68/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S68" s="23">
+      <c r="S68" s="19">
         <f>IF('Porcentaje de Notas'!S68="","",('Porcentaje de Notas'!S68/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T68" s="37">
+      <c r="T68" s="49">
         <f t="shared" si="0"/>
         <v>16.75</v>
       </c>
     </row>
     <row r="69" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C69" s="23">
+      <c r="C69" s="19">
         <v>65</v>
       </c>
-      <c r="D69" s="23">
+      <c r="D69" s="19">
         <v>202531736</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F69" s="35">
+      <c r="F69" s="31">
         <f>IF('Porcentaje de Notas'!F69="","",('Porcentaje de Notas'!F69/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G69" s="23">
+      <c r="G69" s="19">
         <f>IF('Porcentaje de Notas'!G69="","",('Porcentaje de Notas'!G69/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H69" s="23">
+      <c r="H69" s="19">
         <f>IF('Porcentaje de Notas'!H69="","",('Porcentaje de Notas'!H69/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I69" s="36">
+      <c r="I69" s="32">
         <f>IF('Porcentaje de Notas'!I69="","",('Porcentaje de Notas'!I69/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="31">
         <f>IF('Porcentaje de Notas'!J69="","",('Porcentaje de Notas'!J69/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K69" s="23">
+      <c r="K69" s="19">
         <f>IF('Porcentaje de Notas'!K69="","",('Porcentaje de Notas'!K69/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L69" s="23">
+      <c r="L69" s="19">
         <f>IF('Porcentaje de Notas'!L69="","",('Porcentaje de Notas'!L69/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M69" s="23">
+      <c r="M69" s="19">
         <f>IF('Porcentaje de Notas'!M69="","",('Porcentaje de Notas'!M69/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N69" s="23">
+      <c r="N69" s="19">
         <f>IF('Porcentaje de Notas'!N69="","",('Porcentaje de Notas'!N69/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O69" s="23">
+      <c r="O69" s="19">
         <f>IF('Porcentaje de Notas'!O69="","",('Porcentaje de Notas'!O69/100)*$O$3)</f>
         <v>1.2</v>
       </c>
-      <c r="P69" s="23">
+      <c r="P69" s="19">
         <f>IF('Porcentaje de Notas'!P69="","",('Porcentaje de Notas'!P69/100)*$P$3)</f>
         <v>1.3</v>
       </c>
-      <c r="Q69" s="23">
+      <c r="Q69" s="19">
         <f>IF('Porcentaje de Notas'!Q69="","",('Porcentaje de Notas'!Q69/100)*$Q$3)</f>
         <v>0.8</v>
       </c>
-      <c r="R69" s="23">
+      <c r="R69" s="19">
         <f>IF('Porcentaje de Notas'!R69="","",('Porcentaje de Notas'!R69/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S69" s="23">
+      <c r="S69" s="19">
         <f>IF('Porcentaje de Notas'!S69="","",('Porcentaje de Notas'!S69/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T69" s="37">
+      <c r="T69" s="49">
         <f t="shared" si="0"/>
         <v>14.3</v>
       </c>
     </row>
     <row r="70" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C70" s="23">
+      <c r="C70" s="19">
         <v>66</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D70" s="19">
         <v>202531778</v>
       </c>
-      <c r="E70" s="24" t="s">
+      <c r="E70" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F70" s="35">
+      <c r="F70" s="31">
         <f>IF('Porcentaje de Notas'!F70="","",('Porcentaje de Notas'!F70/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="19">
         <f>IF('Porcentaje de Notas'!G70="","",('Porcentaje de Notas'!G70/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H70" s="23">
+      <c r="H70" s="19">
         <f>IF('Porcentaje de Notas'!H70="","",('Porcentaje de Notas'!H70/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I70" s="36">
+      <c r="I70" s="32">
         <f>IF('Porcentaje de Notas'!I70="","",('Porcentaje de Notas'!I70/100)*$I$3)</f>
         <v>0.45</v>
       </c>
-      <c r="J70" s="35">
+      <c r="J70" s="31">
         <f>IF('Porcentaje de Notas'!J70="","",('Porcentaje de Notas'!J70/100)*$J$3)</f>
         <v>0.75</v>
       </c>
-      <c r="K70" s="23">
+      <c r="K70" s="19">
         <f>IF('Porcentaje de Notas'!K70="","",('Porcentaje de Notas'!K70/100)*$K$3)</f>
         <v>0.85</v>
       </c>
-      <c r="L70" s="23">
+      <c r="L70" s="19">
         <f>IF('Porcentaje de Notas'!L70="","",('Porcentaje de Notas'!L70/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M70" s="23">
+      <c r="M70" s="19">
         <f>IF('Porcentaje de Notas'!M70="","",('Porcentaje de Notas'!M70/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N70" s="23">
+      <c r="N70" s="19">
         <f>IF('Porcentaje de Notas'!N70="","",('Porcentaje de Notas'!N70/100)*$N$3)</f>
         <v>1.4</v>
       </c>
-      <c r="O70" s="23">
+      <c r="O70" s="19">
         <f>IF('Porcentaje de Notas'!O70="","",('Porcentaje de Notas'!O70/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P70" s="23">
+      <c r="P70" s="19">
         <f>IF('Porcentaje de Notas'!P70="","",('Porcentaje de Notas'!P70/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q70" s="23">
+      <c r="Q70" s="19">
         <f>IF('Porcentaje de Notas'!Q70="","",('Porcentaje de Notas'!Q70/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R70" s="23">
+      <c r="R70" s="19">
         <f>IF('Porcentaje de Notas'!R70="","",('Porcentaje de Notas'!R70/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S70" s="23">
+      <c r="S70" s="19">
         <f>IF('Porcentaje de Notas'!S70="","",('Porcentaje de Notas'!S70/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T70" s="37">
+      <c r="T70" s="49">
         <f t="shared" ref="T70:T77" si="1">SUM(F70:S70)</f>
         <v>18.25</v>
       </c>
     </row>
     <row r="71" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C71" s="23">
+      <c r="C71" s="19">
         <v>67</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D71" s="19">
         <v>202531844</v>
       </c>
-      <c r="E71" s="24" t="s">
+      <c r="E71" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F71" s="35">
+      <c r="F71" s="31">
         <f>IF('Porcentaje de Notas'!F71="","",('Porcentaje de Notas'!F71/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G71" s="23">
+      <c r="G71" s="19">
         <f>IF('Porcentaje de Notas'!G71="","",('Porcentaje de Notas'!G71/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H71" s="23">
+      <c r="H71" s="19">
         <f>IF('Porcentaje de Notas'!H71="","",('Porcentaje de Notas'!H71/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I71" s="36">
+      <c r="I71" s="32">
         <f>IF('Porcentaje de Notas'!I71="","",('Porcentaje de Notas'!I71/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J71" s="35">
+      <c r="J71" s="31">
         <f>IF('Porcentaje de Notas'!J71="","",('Porcentaje de Notas'!J71/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K71" s="23">
+      <c r="K71" s="19">
         <f>IF('Porcentaje de Notas'!K71="","",('Porcentaje de Notas'!K71/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L71" s="23">
+      <c r="L71" s="19">
         <f>IF('Porcentaje de Notas'!L71="","",('Porcentaje de Notas'!L71/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M71" s="23">
+      <c r="M71" s="19">
         <f>IF('Porcentaje de Notas'!M71="","",('Porcentaje de Notas'!M71/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N71" s="23">
+      <c r="N71" s="19">
         <f>IF('Porcentaje de Notas'!N71="","",('Porcentaje de Notas'!N71/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O71" s="23">
+      <c r="O71" s="19">
         <f>IF('Porcentaje de Notas'!O71="","",('Porcentaje de Notas'!O71/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P71" s="23">
+      <c r="P71" s="19">
         <f>IF('Porcentaje de Notas'!P71="","",('Porcentaje de Notas'!P71/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q71" s="23">
+      <c r="Q71" s="19">
         <f>IF('Porcentaje de Notas'!Q71="","",('Porcentaje de Notas'!Q71/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R71" s="23">
+      <c r="R71" s="19">
         <f>IF('Porcentaje de Notas'!R71="","",('Porcentaje de Notas'!R71/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S71" s="23">
+      <c r="S71" s="19">
         <f>IF('Porcentaje de Notas'!S71="","",('Porcentaje de Notas'!S71/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T71" s="37">
+      <c r="T71" s="49">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
     <row r="72" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C72" s="23">
+      <c r="C72" s="19">
         <v>68</v>
       </c>
-      <c r="D72" s="23">
+      <c r="D72" s="19">
         <v>202531883</v>
       </c>
-      <c r="E72" s="24" t="s">
+      <c r="E72" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F72" s="35">
+      <c r="F72" s="31">
         <f>IF('Porcentaje de Notas'!F72="","",('Porcentaje de Notas'!F72/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G72" s="23">
+      <c r="G72" s="19">
         <f>IF('Porcentaje de Notas'!G72="","",('Porcentaje de Notas'!G72/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H72" s="23">
+      <c r="H72" s="19">
         <f>IF('Porcentaje de Notas'!H72="","",('Porcentaje de Notas'!H72/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I72" s="36">
+      <c r="I72" s="32">
         <f>IF('Porcentaje de Notas'!I72="","",('Porcentaje de Notas'!I72/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J72" s="35">
+      <c r="J72" s="31">
         <f>IF('Porcentaje de Notas'!J72="","",('Porcentaje de Notas'!J72/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K72" s="23">
+      <c r="K72" s="19">
         <f>IF('Porcentaje de Notas'!K72="","",('Porcentaje de Notas'!K72/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L72" s="23">
+      <c r="L72" s="19">
         <f>IF('Porcentaje de Notas'!L72="","",('Porcentaje de Notas'!L72/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M72" s="23">
+      <c r="M72" s="19">
         <f>IF('Porcentaje de Notas'!M72="","",('Porcentaje de Notas'!M72/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N72" s="23">
+      <c r="N72" s="19">
         <f>IF('Porcentaje de Notas'!N72="","",('Porcentaje de Notas'!N72/100)*$N$3)</f>
         <v>1.8</v>
       </c>
-      <c r="O72" s="23">
+      <c r="O72" s="19">
         <f>IF('Porcentaje de Notas'!O72="","",('Porcentaje de Notas'!O72/100)*$O$3)</f>
         <v>1.9</v>
       </c>
-      <c r="P72" s="23">
+      <c r="P72" s="19">
         <f>IF('Porcentaje de Notas'!P72="","",('Porcentaje de Notas'!P72/100)*$P$3)</f>
         <v>1.7</v>
       </c>
-      <c r="Q72" s="23">
+      <c r="Q72" s="19">
         <f>IF('Porcentaje de Notas'!Q72="","",('Porcentaje de Notas'!Q72/100)*$Q$3)</f>
         <v>0.95</v>
       </c>
-      <c r="R72" s="23">
+      <c r="R72" s="19">
         <f>IF('Porcentaje de Notas'!R72="","",('Porcentaje de Notas'!R72/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S72" s="23">
+      <c r="S72" s="19">
         <f>IF('Porcentaje de Notas'!S72="","",('Porcentaje de Notas'!S72/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T72" s="37">
+      <c r="T72" s="49">
         <f t="shared" si="1"/>
         <v>17.199999999999996</v>
       </c>
     </row>
     <row r="73" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C73" s="23">
+      <c r="C73" s="19">
         <v>69</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D73" s="19">
         <v>202531947</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F73" s="35">
+      <c r="F73" s="31">
         <f>IF('Porcentaje de Notas'!F73="","",('Porcentaje de Notas'!F73/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G73" s="23">
+      <c r="G73" s="19">
         <f>IF('Porcentaje de Notas'!G73="","",('Porcentaje de Notas'!G73/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H73" s="23">
+      <c r="H73" s="19">
         <f>IF('Porcentaje de Notas'!H73="","",('Porcentaje de Notas'!H73/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I73" s="36">
+      <c r="I73" s="32">
         <f>IF('Porcentaje de Notas'!I73="","",('Porcentaje de Notas'!I73/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J73" s="35">
+      <c r="J73" s="31">
         <f>IF('Porcentaje de Notas'!J73="","",('Porcentaje de Notas'!J73/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K73" s="23">
+      <c r="K73" s="19">
         <f>IF('Porcentaje de Notas'!K73="","",('Porcentaje de Notas'!K73/100)*$K$3)</f>
         <v>0.75</v>
       </c>
-      <c r="L73" s="23">
+      <c r="L73" s="19">
         <f>IF('Porcentaje de Notas'!L73="","",('Porcentaje de Notas'!L73/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M73" s="23">
+      <c r="M73" s="19">
         <f>IF('Porcentaje de Notas'!M73="","",('Porcentaje de Notas'!M73/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N73" s="23">
+      <c r="N73" s="19">
         <f>IF('Porcentaje de Notas'!N73="","",('Porcentaje de Notas'!N73/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O73" s="23">
+      <c r="O73" s="19">
         <f>IF('Porcentaje de Notas'!O73="","",('Porcentaje de Notas'!O73/100)*$O$3)</f>
         <v>1.8</v>
       </c>
-      <c r="P73" s="23">
+      <c r="P73" s="19">
         <f>IF('Porcentaje de Notas'!P73="","",('Porcentaje de Notas'!P73/100)*$P$3)</f>
         <v>1.4</v>
       </c>
-      <c r="Q73" s="23">
+      <c r="Q73" s="19">
         <f>IF('Porcentaje de Notas'!Q73="","",('Porcentaje de Notas'!Q73/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R73" s="23">
+      <c r="R73" s="19">
         <f>IF('Porcentaje de Notas'!R73="","",('Porcentaje de Notas'!R73/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S73" s="23">
+      <c r="S73" s="19">
         <f>IF('Porcentaje de Notas'!S73="","",('Porcentaje de Notas'!S73/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T73" s="37">
+      <c r="T73" s="49">
         <f t="shared" si="1"/>
         <v>9.2999999999999989</v>
       </c>
     </row>
     <row r="74" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C74" s="23">
+      <c r="C74" s="19">
         <v>70</v>
       </c>
-      <c r="D74" s="23">
+      <c r="D74" s="19">
         <v>202532062</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="E74" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F74" s="35">
+      <c r="F74" s="31">
         <f>IF('Porcentaje de Notas'!F74="","",('Porcentaje de Notas'!F74/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G74" s="23">
+      <c r="G74" s="19">
         <f>IF('Porcentaje de Notas'!G74="","",('Porcentaje de Notas'!G74/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H74" s="23">
+      <c r="H74" s="19">
         <f>IF('Porcentaje de Notas'!H74="","",('Porcentaje de Notas'!H74/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I74" s="36">
+      <c r="I74" s="32">
         <f>IF('Porcentaje de Notas'!I74="","",('Porcentaje de Notas'!I74/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J74" s="35">
+      <c r="J74" s="31">
         <f>IF('Porcentaje de Notas'!J74="","",('Porcentaje de Notas'!J74/100)*$J$3)</f>
         <v>0.85</v>
       </c>
-      <c r="K74" s="23">
+      <c r="K74" s="19">
         <f>IF('Porcentaje de Notas'!K74="","",('Porcentaje de Notas'!K74/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L74" s="23">
+      <c r="L74" s="19">
         <f>IF('Porcentaje de Notas'!L74="","",('Porcentaje de Notas'!L74/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M74" s="23">
+      <c r="M74" s="19">
         <f>IF('Porcentaje de Notas'!M74="","",('Porcentaje de Notas'!M74/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N74" s="23">
+      <c r="N74" s="19">
         <f>IF('Porcentaje de Notas'!N74="","",('Porcentaje de Notas'!N74/100)*$N$3)</f>
         <v>1</v>
       </c>
-      <c r="O74" s="23">
+      <c r="O74" s="19">
         <f>IF('Porcentaje de Notas'!O74="","",('Porcentaje de Notas'!O74/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P74" s="23">
+      <c r="P74" s="19">
         <f>IF('Porcentaje de Notas'!P74="","",('Porcentaje de Notas'!P74/100)*$P$3)</f>
         <v>0.4</v>
       </c>
-      <c r="Q74" s="23">
+      <c r="Q74" s="19">
         <f>IF('Porcentaje de Notas'!Q74="","",('Porcentaje de Notas'!Q74/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R74" s="23">
+      <c r="R74" s="19">
         <f>IF('Porcentaje de Notas'!R74="","",('Porcentaje de Notas'!R74/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S74" s="23">
+      <c r="S74" s="19">
         <f>IF('Porcentaje de Notas'!S74="","",('Porcentaje de Notas'!S74/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T74" s="37">
+      <c r="T74" s="49">
         <f t="shared" si="1"/>
         <v>13.75</v>
       </c>
     </row>
     <row r="75" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C75" s="23">
+      <c r="C75" s="19">
         <v>71</v>
       </c>
-      <c r="D75" s="23">
+      <c r="D75" s="19">
         <v>202532079</v>
       </c>
-      <c r="E75" s="24" t="s">
+      <c r="E75" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F75" s="35">
+      <c r="F75" s="31">
         <f>IF('Porcentaje de Notas'!F75="","",('Porcentaje de Notas'!F75/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G75" s="23">
+      <c r="G75" s="19">
         <f>IF('Porcentaje de Notas'!G75="","",('Porcentaje de Notas'!G75/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H75" s="23">
+      <c r="H75" s="19">
         <f>IF('Porcentaje de Notas'!H75="","",('Porcentaje de Notas'!H75/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I75" s="36">
+      <c r="I75" s="32">
         <f>IF('Porcentaje de Notas'!I75="","",('Porcentaje de Notas'!I75/100)*$I$3)</f>
         <v>0</v>
       </c>
-      <c r="J75" s="35">
+      <c r="J75" s="31">
         <f>IF('Porcentaje de Notas'!J75="","",('Porcentaje de Notas'!J75/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K75" s="23">
+      <c r="K75" s="19">
         <f>IF('Porcentaje de Notas'!K75="","",('Porcentaje de Notas'!K75/100)*$K$3)</f>
         <v>0.5</v>
       </c>
-      <c r="L75" s="23">
+      <c r="L75" s="19">
         <f>IF('Porcentaje de Notas'!L75="","",('Porcentaje de Notas'!L75/100)*$L$3)</f>
         <v>0</v>
       </c>
-      <c r="M75" s="23">
+      <c r="M75" s="19">
         <f>IF('Porcentaje de Notas'!M75="","",('Porcentaje de Notas'!M75/100)*$M$3)</f>
         <v>0</v>
       </c>
-      <c r="N75" s="23">
+      <c r="N75" s="19">
         <f>IF('Porcentaje de Notas'!N75="","",('Porcentaje de Notas'!N75/100)*$N$3)</f>
         <v>0</v>
       </c>
-      <c r="O75" s="23">
+      <c r="O75" s="19">
         <f>IF('Porcentaje de Notas'!O75="","",('Porcentaje de Notas'!O75/100)*$O$3)</f>
         <v>0</v>
       </c>
-      <c r="P75" s="23">
+      <c r="P75" s="19">
         <f>IF('Porcentaje de Notas'!P75="","",('Porcentaje de Notas'!P75/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q75" s="23">
+      <c r="Q75" s="19">
         <f>IF('Porcentaje de Notas'!Q75="","",('Porcentaje de Notas'!Q75/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R75" s="23">
+      <c r="R75" s="19">
         <f>IF('Porcentaje de Notas'!R75="","",('Porcentaje de Notas'!R75/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S75" s="23">
+      <c r="S75" s="19">
         <f>IF('Porcentaje de Notas'!S75="","",('Porcentaje de Notas'!S75/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T75" s="37">
+      <c r="T75" s="49">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="3:20" x14ac:dyDescent="0.35">
-      <c r="C76" s="23">
+      <c r="C76" s="19">
         <v>72</v>
       </c>
-      <c r="D76" s="23">
+      <c r="D76" s="19">
         <v>202530466</v>
       </c>
-      <c r="E76" s="24" t="s">
+      <c r="E76" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F76" s="35">
+      <c r="F76" s="31">
         <f>IF('Porcentaje de Notas'!F76="","",('Porcentaje de Notas'!F76/100)*$F$3)</f>
         <v>0.5</v>
       </c>
-      <c r="G76" s="23">
+      <c r="G76" s="19">
         <f>IF('Porcentaje de Notas'!G76="","",('Porcentaje de Notas'!G76/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H76" s="23">
+      <c r="H76" s="19">
         <f>IF('Porcentaje de Notas'!H76="","",('Porcentaje de Notas'!H76/100)*$H$3)</f>
         <v>0.5</v>
       </c>
-      <c r="I76" s="36">
+      <c r="I76" s="32">
         <f>IF('Porcentaje de Notas'!I76="","",('Porcentaje de Notas'!I76/100)*$I$3)</f>
         <v>0.5</v>
       </c>
-      <c r="J76" s="35">
+      <c r="J76" s="31">
         <f>IF('Porcentaje de Notas'!J76="","",('Porcentaje de Notas'!J76/100)*$J$3)</f>
         <v>1</v>
       </c>
-      <c r="K76" s="23">
+      <c r="K76" s="19">
         <f>IF('Porcentaje de Notas'!K76="","",('Porcentaje de Notas'!K76/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L76" s="23">
+      <c r="L76" s="19">
         <f>IF('Porcentaje de Notas'!L76="","",('Porcentaje de Notas'!L76/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M76" s="23">
+      <c r="M76" s="19">
         <f>IF('Porcentaje de Notas'!M76="","",('Porcentaje de Notas'!M76/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N76" s="23">
+      <c r="N76" s="19">
         <f>IF('Porcentaje de Notas'!N76="","",('Porcentaje de Notas'!N76/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O76" s="23">
+      <c r="O76" s="19">
         <f>IF('Porcentaje de Notas'!O76="","",('Porcentaje de Notas'!O76/100)*$O$3)</f>
         <v>2</v>
       </c>
-      <c r="P76" s="23">
+      <c r="P76" s="19">
         <f>IF('Porcentaje de Notas'!P76="","",('Porcentaje de Notas'!P76/100)*$P$3)</f>
         <v>2</v>
       </c>
-      <c r="Q76" s="23">
+      <c r="Q76" s="19">
         <f>IF('Porcentaje de Notas'!Q76="","",('Porcentaje de Notas'!Q76/100)*$Q$3)</f>
         <v>1</v>
       </c>
-      <c r="R76" s="23">
+      <c r="R76" s="19">
         <f>IF('Porcentaje de Notas'!R76="","",('Porcentaje de Notas'!R76/100)*$R$3)</f>
         <v>1.5</v>
       </c>
-      <c r="S76" s="23">
+      <c r="S76" s="19">
         <f>IF('Porcentaje de Notas'!S76="","",('Porcentaje de Notas'!S76/100)*$S$3)</f>
         <v>5</v>
       </c>
-      <c r="T76" s="37">
+      <c r="T76" s="49">
         <f t="shared" si="1"/>
         <v>19.5</v>
       </c>
     </row>
     <row r="77" spans="3:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C77" s="23">
+      <c r="C77" s="19">
         <v>73</v>
       </c>
-      <c r="D77" s="23">
+      <c r="D77" s="19">
         <v>202030192</v>
       </c>
-      <c r="E77" s="24" t="s">
+      <c r="E77" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F77" s="40">
+      <c r="F77" s="33">
         <f>IF('Porcentaje de Notas'!F77="","",('Porcentaje de Notas'!F77/100)*$F$3)</f>
         <v>0</v>
       </c>
-      <c r="G77" s="41">
+      <c r="G77" s="34">
         <f>IF('Porcentaje de Notas'!G77="","",('Porcentaje de Notas'!G77/100)*$G$3)</f>
         <v>0</v>
       </c>
-      <c r="H77" s="41">
+      <c r="H77" s="34">
         <f>IF('Porcentaje de Notas'!H77="","",('Porcentaje de Notas'!H77/100)*$H$3)</f>
         <v>0.25</v>
       </c>
-      <c r="I77" s="42">
+      <c r="I77" s="35">
         <f>IF('Porcentaje de Notas'!I77="","",('Porcentaje de Notas'!I77/100)*$I$3)</f>
         <v>0.375</v>
       </c>
-      <c r="J77" s="40">
+      <c r="J77" s="33">
         <f>IF('Porcentaje de Notas'!J77="","",('Porcentaje de Notas'!J77/100)*$J$3)</f>
         <v>0</v>
       </c>
-      <c r="K77" s="41">
+      <c r="K77" s="34">
         <f>IF('Porcentaje de Notas'!K77="","",('Porcentaje de Notas'!K77/100)*$K$3)</f>
         <v>1</v>
       </c>
-      <c r="L77" s="41">
+      <c r="L77" s="34">
         <f>IF('Porcentaje de Notas'!L77="","",('Porcentaje de Notas'!L77/100)*$L$3)</f>
         <v>1</v>
       </c>
-      <c r="M77" s="41">
+      <c r="M77" s="34">
         <f>IF('Porcentaje de Notas'!M77="","",('Porcentaje de Notas'!M77/100)*$M$3)</f>
         <v>1.5</v>
       </c>
-      <c r="N77" s="41">
+      <c r="N77" s="34">
         <f>IF('Porcentaje de Notas'!N77="","",('Porcentaje de Notas'!N77/100)*$N$3)</f>
         <v>2</v>
       </c>
-      <c r="O77" s="41">
+      <c r="O77" s="34">
         <f>IF('Porcentaje de Notas'!O77="","",('Porcentaje de Notas'!O77/100)*$O$3)</f>
         <v>1.7</v>
       </c>
-      <c r="P77" s="41">
+      <c r="P77" s="34">
         <f>IF('Porcentaje de Notas'!P77="","",('Porcentaje de Notas'!P77/100)*$P$3)</f>
         <v>0</v>
       </c>
-      <c r="Q77" s="41">
+      <c r="Q77" s="34">
         <f>IF('Porcentaje de Notas'!Q77="","",('Porcentaje de Notas'!Q77/100)*$Q$3)</f>
         <v>0</v>
       </c>
-      <c r="R77" s="41">
+      <c r="R77" s="34">
         <f>IF('Porcentaje de Notas'!R77="","",('Porcentaje de Notas'!R77/100)*$R$3)</f>
         <v>0</v>
       </c>
-      <c r="S77" s="41">
+      <c r="S77" s="34">
         <f>IF('Porcentaje de Notas'!S77="","",('Porcentaje de Notas'!S77/100)*$S$3)</f>
         <v>0</v>
       </c>
-      <c r="T77" s="37">
+      <c r="T77" s="49">
         <f t="shared" si="1"/>
         <v>7.8250000000000002</v>
       </c>
@@ -9578,56 +9574,54 @@
     <col min="4" max="4" width="12.6328125" customWidth="1"/>
     <col min="5" max="5" width="33.90625" customWidth="1"/>
     <col min="6" max="9" width="7.453125" customWidth="1"/>
-    <col min="10" max="16" width="9.6328125" customWidth="1"/>
-    <col min="17" max="17" width="9.6328125" style="19" customWidth="1"/>
-    <col min="18" max="20" width="9.6328125" customWidth="1"/>
+    <col min="10" max="20" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:25" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="3:25" s="1" customFormat="1" ht="103.5" x14ac:dyDescent="0.35">
-      <c r="C2" s="43"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="J2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="L2" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="50" t="s">
+      <c r="P2" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="R2" s="50" t="s">
+      <c r="R2" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="S2" s="50" t="s">
+      <c r="S2" s="41" t="s">
         <v>93</v>
       </c>
       <c r="T2" s="15" t="s">
@@ -9639,9 +9633,9 @@
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="C3" s="44"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="39" t="s">
         <v>98</v>
       </c>
       <c r="F3" s="8">
@@ -9677,7 +9671,7 @@
       <c r="P3" s="8">
         <v>2</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="8">
         <v>1</v>
       </c>
       <c r="R3" s="8">
@@ -9692,7 +9686,7 @@
       </c>
     </row>
     <row r="4" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="38" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -9701,46 +9695,46 @@
       <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="L4" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="M4" s="21" t="s">
+      <c r="L4" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="M4" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="N4" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="Q4" s="21" t="s">
+      <c r="Q4" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" s="17" t="s">
         <v>94</v>
       </c>
       <c r="T4" s="16" t="s">
@@ -9801,7 +9795,7 @@
         <f>[1]Hoja1!P5</f>
         <v>100</v>
       </c>
-      <c r="Q5" s="17">
+      <c r="Q5" s="6">
         <f>[1]Hoja1!Q5</f>
         <v>0</v>
       </c>
@@ -9869,7 +9863,7 @@
         <f>[1]Hoja1!P6</f>
         <v>100</v>
       </c>
-      <c r="Q6" s="17">
+      <c r="Q6" s="6">
         <f>[1]Hoja1!Q6</f>
         <v>100</v>
       </c>
@@ -9937,7 +9931,7 @@
         <f>[1]Hoja1!P7</f>
         <v>85</v>
       </c>
-      <c r="Q7" s="17">
+      <c r="Q7" s="6">
         <f>[1]Hoja1!Q7</f>
         <v>80</v>
       </c>
@@ -10005,7 +9999,7 @@
         <f>[1]Hoja1!P8</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="17">
+      <c r="Q8" s="6">
         <f>[1]Hoja1!Q8</f>
         <v>0</v>
       </c>
@@ -10073,7 +10067,7 @@
         <f>[1]Hoja1!P9</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="17">
+      <c r="Q9" s="6">
         <f>[1]Hoja1!Q9</f>
         <v>100</v>
       </c>
@@ -10141,7 +10135,7 @@
         <f>[1]Hoja1!P10</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="6">
         <f>[1]Hoja1!Q10</f>
         <v>0</v>
       </c>
@@ -10209,7 +10203,7 @@
         <f>[1]Hoja1!P11</f>
         <v>65</v>
       </c>
-      <c r="Q11" s="17">
+      <c r="Q11" s="6">
         <f>[1]Hoja1!Q11</f>
         <v>80</v>
       </c>
@@ -10277,7 +10271,7 @@
         <f>[1]Hoja1!P12</f>
         <v>70</v>
       </c>
-      <c r="Q12" s="17">
+      <c r="Q12" s="6">
         <f>[1]Hoja1!Q12</f>
         <v>80</v>
       </c>
@@ -10345,7 +10339,7 @@
         <f>[1]Hoja1!P13</f>
         <v>80</v>
       </c>
-      <c r="Q13" s="17">
+      <c r="Q13" s="6">
         <f>[1]Hoja1!Q13</f>
         <v>100</v>
       </c>
@@ -10413,7 +10407,7 @@
         <f>[1]Hoja1!P14</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="17">
+      <c r="Q14" s="6">
         <f>[1]Hoja1!Q14</f>
         <v>0</v>
       </c>
@@ -10481,7 +10475,7 @@
         <f>[1]Hoja1!P15</f>
         <v>30</v>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="6">
         <f>[1]Hoja1!Q15</f>
         <v>0</v>
       </c>
@@ -10549,7 +10543,7 @@
         <f>[1]Hoja1!P16</f>
         <v>50</v>
       </c>
-      <c r="Q16" s="17">
+      <c r="Q16" s="6">
         <f>[1]Hoja1!Q16</f>
         <v>0</v>
       </c>
@@ -10617,7 +10611,7 @@
         <f>[1]Hoja1!P17</f>
         <v>70</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="6">
         <f>[1]Hoja1!Q17</f>
         <v>100</v>
       </c>
@@ -10685,7 +10679,7 @@
         <f>[1]Hoja1!P18</f>
         <v>100</v>
       </c>
-      <c r="Q18" s="17">
+      <c r="Q18" s="6">
         <f>[1]Hoja1!Q18</f>
         <v>100</v>
       </c>
@@ -10753,7 +10747,7 @@
         <f>[1]Hoja1!P19</f>
         <v>100</v>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="6">
         <f>[1]Hoja1!Q19</f>
         <v>0</v>
       </c>
@@ -10821,7 +10815,7 @@
         <f>[1]Hoja1!P20</f>
         <v>85</v>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="6">
         <f>[1]Hoja1!Q20</f>
         <v>80</v>
       </c>
@@ -10889,7 +10883,7 @@
         <f>[1]Hoja1!P21</f>
         <v>100</v>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="6">
         <f>[1]Hoja1!Q21</f>
         <v>100</v>
       </c>
@@ -10957,7 +10951,7 @@
         <f>[1]Hoja1!P22</f>
         <v>45</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="6">
         <f>[1]Hoja1!Q22</f>
         <v>80</v>
       </c>
@@ -11025,7 +11019,7 @@
         <f>[1]Hoja1!P23</f>
         <v>90</v>
       </c>
-      <c r="Q23" s="17">
+      <c r="Q23" s="6">
         <f>[1]Hoja1!Q23</f>
         <v>0</v>
       </c>
@@ -11093,7 +11087,7 @@
         <f>[1]Hoja1!P24</f>
         <v>90</v>
       </c>
-      <c r="Q24" s="17">
+      <c r="Q24" s="6">
         <f>[1]Hoja1!Q24</f>
         <v>100</v>
       </c>
@@ -11161,7 +11155,7 @@
         <f>[1]Hoja1!P25</f>
         <v>70</v>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="6">
         <f>[1]Hoja1!Q25</f>
         <v>80</v>
       </c>
@@ -11229,7 +11223,7 @@
         <f>[1]Hoja1!P26</f>
         <v>100</v>
       </c>
-      <c r="Q26" s="17">
+      <c r="Q26" s="6">
         <f>[1]Hoja1!Q26</f>
         <v>80</v>
       </c>
@@ -11297,7 +11291,7 @@
         <f>[1]Hoja1!P27</f>
         <v>100</v>
       </c>
-      <c r="Q27" s="17">
+      <c r="Q27" s="6">
         <f>[1]Hoja1!Q27</f>
         <v>0</v>
       </c>
@@ -11365,7 +11359,7 @@
         <f>[1]Hoja1!P28</f>
         <v>90</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="6">
         <f>[1]Hoja1!Q28</f>
         <v>0</v>
       </c>
@@ -11433,7 +11427,7 @@
         <f>[1]Hoja1!P29</f>
         <v>100</v>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="6">
         <f>[1]Hoja1!Q29</f>
         <v>80</v>
       </c>
@@ -11501,7 +11495,7 @@
         <f>[1]Hoja1!P30</f>
         <v>60</v>
       </c>
-      <c r="Q30" s="17">
+      <c r="Q30" s="6">
         <f>[1]Hoja1!Q30</f>
         <v>0</v>
       </c>
@@ -11569,7 +11563,7 @@
         <f>[1]Hoja1!P31</f>
         <v>100</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="6">
         <f>[1]Hoja1!Q31</f>
         <v>80</v>
       </c>
@@ -11637,7 +11631,7 @@
         <f>[1]Hoja1!P32</f>
         <v>100</v>
       </c>
-      <c r="Q32" s="17">
+      <c r="Q32" s="6">
         <f>[1]Hoja1!Q32</f>
         <v>90</v>
       </c>
@@ -11705,7 +11699,7 @@
         <f>[1]Hoja1!P33</f>
         <v>50</v>
       </c>
-      <c r="Q33" s="17">
+      <c r="Q33" s="6">
         <f>[1]Hoja1!Q33</f>
         <v>80</v>
       </c>
@@ -11773,7 +11767,7 @@
         <f>[1]Hoja1!P34</f>
         <v>65</v>
       </c>
-      <c r="Q34" s="17">
+      <c r="Q34" s="6">
         <f>[1]Hoja1!Q34</f>
         <v>80</v>
       </c>
@@ -11841,7 +11835,7 @@
         <f>[1]Hoja1!P35</f>
         <v>60</v>
       </c>
-      <c r="Q35" s="17">
+      <c r="Q35" s="6">
         <f>[1]Hoja1!Q35</f>
         <v>100</v>
       </c>
@@ -11909,7 +11903,7 @@
         <f>[1]Hoja1!P36</f>
         <v>80</v>
       </c>
-      <c r="Q36" s="17">
+      <c r="Q36" s="6">
         <f>[1]Hoja1!Q36</f>
         <v>100</v>
       </c>
@@ -11977,7 +11971,7 @@
         <f>[1]Hoja1!P37</f>
         <v>45</v>
       </c>
-      <c r="Q37" s="17">
+      <c r="Q37" s="6">
         <f>[1]Hoja1!Q37</f>
         <v>80</v>
       </c>
@@ -12045,7 +12039,7 @@
         <f>[1]Hoja1!P38</f>
         <v>100</v>
       </c>
-      <c r="Q38" s="17">
+      <c r="Q38" s="6">
         <f>[1]Hoja1!Q38</f>
         <v>95</v>
       </c>
@@ -12113,7 +12107,7 @@
         <f>[1]Hoja1!P39</f>
         <v>80</v>
       </c>
-      <c r="Q39" s="17">
+      <c r="Q39" s="6">
         <f>[1]Hoja1!Q39</f>
         <v>100</v>
       </c>
@@ -12181,7 +12175,7 @@
         <f>[1]Hoja1!P40</f>
         <v>80</v>
       </c>
-      <c r="Q40" s="17">
+      <c r="Q40" s="6">
         <f>[1]Hoja1!Q40</f>
         <v>0</v>
       </c>
@@ -12249,7 +12243,7 @@
         <f>[1]Hoja1!P41</f>
         <v>0</v>
       </c>
-      <c r="Q41" s="17">
+      <c r="Q41" s="6">
         <f>[1]Hoja1!Q41</f>
         <v>0</v>
       </c>
@@ -12317,7 +12311,7 @@
         <f>[1]Hoja1!P42</f>
         <v>65</v>
       </c>
-      <c r="Q42" s="17">
+      <c r="Q42" s="6">
         <f>[1]Hoja1!Q42</f>
         <v>80</v>
       </c>
@@ -12385,7 +12379,7 @@
         <f>[1]Hoja1!P43</f>
         <v>0</v>
       </c>
-      <c r="Q43" s="17">
+      <c r="Q43" s="6">
         <f>[1]Hoja1!Q43</f>
         <v>50</v>
       </c>
@@ -12453,7 +12447,7 @@
         <f>[1]Hoja1!P44</f>
         <v>70</v>
       </c>
-      <c r="Q44" s="17">
+      <c r="Q44" s="6">
         <f>[1]Hoja1!Q44</f>
         <v>0</v>
       </c>
@@ -12521,7 +12515,7 @@
         <f>[1]Hoja1!P45</f>
         <v>0</v>
       </c>
-      <c r="Q45" s="17">
+      <c r="Q45" s="6">
         <f>[1]Hoja1!Q45</f>
         <v>0</v>
       </c>
@@ -12589,7 +12583,7 @@
         <f>[1]Hoja1!P46</f>
         <v>50</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="6">
         <f>[1]Hoja1!Q46</f>
         <v>80</v>
       </c>
@@ -12657,7 +12651,7 @@
         <f>[1]Hoja1!P47</f>
         <v>85</v>
       </c>
-      <c r="Q47" s="17">
+      <c r="Q47" s="6">
         <f>[1]Hoja1!Q47</f>
         <v>80</v>
       </c>
@@ -12725,7 +12719,7 @@
         <f>[1]Hoja1!P48</f>
         <v>55</v>
       </c>
-      <c r="Q48" s="17">
+      <c r="Q48" s="6">
         <f>[1]Hoja1!Q48</f>
         <v>100</v>
       </c>
@@ -12793,7 +12787,7 @@
         <f>[1]Hoja1!P49</f>
         <v>65</v>
       </c>
-      <c r="Q49" s="17">
+      <c r="Q49" s="6">
         <f>[1]Hoja1!Q49</f>
         <v>100</v>
       </c>
@@ -12861,7 +12855,7 @@
         <f>[1]Hoja1!P50</f>
         <v>70</v>
       </c>
-      <c r="Q50" s="17">
+      <c r="Q50" s="6">
         <f>[1]Hoja1!Q50</f>
         <v>100</v>
       </c>
@@ -12929,7 +12923,7 @@
         <f>[1]Hoja1!P51</f>
         <v>55</v>
       </c>
-      <c r="Q51" s="17">
+      <c r="Q51" s="6">
         <f>[1]Hoja1!Q51</f>
         <v>100</v>
       </c>
@@ -12997,7 +12991,7 @@
         <f>[1]Hoja1!P52</f>
         <v>55</v>
       </c>
-      <c r="Q52" s="17">
+      <c r="Q52" s="6">
         <f>[1]Hoja1!Q52</f>
         <v>100</v>
       </c>
@@ -13011,73 +13005,73 @@
       </c>
       <c r="T52" s="11"/>
     </row>
-    <row r="53" spans="3:20" s="19" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="18">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C53" s="10">
         <v>49</v>
       </c>
-      <c r="D53" s="17">
+      <c r="D53" s="6">
         <v>202531127</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="17">
+      <c r="F53" s="6">
         <f>[1]Hoja1!F53</f>
         <v>0</v>
       </c>
-      <c r="G53" s="17">
+      <c r="G53" s="6">
         <f>[1]Hoja1!G53</f>
         <v>0</v>
       </c>
-      <c r="H53" s="17">
+      <c r="H53" s="6">
         <f>[1]Hoja1!H53</f>
         <v>100</v>
       </c>
-      <c r="I53" s="17">
+      <c r="I53" s="6">
         <f>[1]Hoja1!I53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="6">
         <f>[1]Hoja1!J53</f>
         <v>0</v>
       </c>
-      <c r="K53" s="17">
+      <c r="K53" s="6">
         <f>[1]Hoja1!K53</f>
         <v>100</v>
       </c>
-      <c r="L53" s="17">
+      <c r="L53" s="6">
         <f>[1]Hoja1!L53</f>
         <v>0</v>
       </c>
-      <c r="M53" s="17">
+      <c r="M53" s="6">
         <f>[1]Hoja1!M53</f>
         <v>100</v>
       </c>
-      <c r="N53" s="17">
+      <c r="N53" s="6">
         <f>[1]Hoja1!N53</f>
         <v>70</v>
       </c>
-      <c r="O53" s="17">
+      <c r="O53" s="6">
         <f>[1]Hoja1!O53</f>
         <v>85</v>
       </c>
-      <c r="P53" s="17">
+      <c r="P53" s="6">
         <f>[1]Hoja1!P53</f>
         <v>85</v>
       </c>
-      <c r="Q53" s="17">
+      <c r="Q53" s="6">
         <f>[1]Hoja1!Q53</f>
         <v>80</v>
       </c>
-      <c r="R53" s="17">
+      <c r="R53" s="6">
         <f>[1]Hoja1!R53</f>
         <v>100</v>
       </c>
-      <c r="S53" s="17">
+      <c r="S53" s="6">
         <f>[1]Hoja1!S53</f>
         <v>100</v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="11"/>
     </row>
     <row r="54" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C54" s="10">
@@ -13133,7 +13127,7 @@
         <f>[1]Hoja1!P54</f>
         <v>100</v>
       </c>
-      <c r="Q54" s="17">
+      <c r="Q54" s="6">
         <f>[1]Hoja1!Q54</f>
         <v>90</v>
       </c>
@@ -13201,7 +13195,7 @@
         <f>[1]Hoja1!P55</f>
         <v>0</v>
       </c>
-      <c r="Q55" s="17">
+      <c r="Q55" s="6">
         <f>[1]Hoja1!Q55</f>
         <v>80</v>
       </c>
@@ -13269,7 +13263,7 @@
         <f>[1]Hoja1!P56</f>
         <v>85</v>
       </c>
-      <c r="Q56" s="17">
+      <c r="Q56" s="6">
         <f>[1]Hoja1!Q56</f>
         <v>95</v>
       </c>
@@ -13337,7 +13331,7 @@
         <f>[1]Hoja1!P57</f>
         <v>50</v>
       </c>
-      <c r="Q57" s="17">
+      <c r="Q57" s="6">
         <f>[1]Hoja1!Q57</f>
         <v>100</v>
       </c>
@@ -13405,7 +13399,7 @@
         <f>[1]Hoja1!P58</f>
         <v>100</v>
       </c>
-      <c r="Q58" s="17">
+      <c r="Q58" s="6">
         <f>[1]Hoja1!Q58</f>
         <v>90</v>
       </c>
@@ -13473,7 +13467,7 @@
         <f>[1]Hoja1!P59</f>
         <v>75</v>
       </c>
-      <c r="Q59" s="17">
+      <c r="Q59" s="6">
         <f>[1]Hoja1!Q59</f>
         <v>80</v>
       </c>
@@ -13541,7 +13535,7 @@
         <f>[1]Hoja1!P60</f>
         <v>90</v>
       </c>
-      <c r="Q60" s="17">
+      <c r="Q60" s="6">
         <f>[1]Hoja1!Q60</f>
         <v>80</v>
       </c>
@@ -13609,7 +13603,7 @@
         <f>[1]Hoja1!P61</f>
         <v>0</v>
       </c>
-      <c r="Q61" s="17">
+      <c r="Q61" s="6">
         <f>[1]Hoja1!Q61</f>
         <v>0</v>
       </c>
@@ -13677,7 +13671,7 @@
         <f>[1]Hoja1!P62</f>
         <v>0</v>
       </c>
-      <c r="Q62" s="17">
+      <c r="Q62" s="6">
         <f>[1]Hoja1!Q62</f>
         <v>0</v>
       </c>
@@ -13745,7 +13739,7 @@
         <f>[1]Hoja1!P63</f>
         <v>65</v>
       </c>
-      <c r="Q63" s="17">
+      <c r="Q63" s="6">
         <f>[1]Hoja1!Q63</f>
         <v>100</v>
       </c>
@@ -13813,7 +13807,7 @@
         <f>[1]Hoja1!P64</f>
         <v>55</v>
       </c>
-      <c r="Q64" s="17">
+      <c r="Q64" s="6">
         <f>[1]Hoja1!Q64</f>
         <v>95</v>
       </c>
@@ -13881,7 +13875,7 @@
         <f>[1]Hoja1!P65</f>
         <v>75</v>
       </c>
-      <c r="Q65" s="17">
+      <c r="Q65" s="6">
         <f>[1]Hoja1!Q65</f>
         <v>0</v>
       </c>
@@ -13939,7 +13933,7 @@
       </c>
       <c r="N66" s="6">
         <f>[1]Hoja1!N66</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O66" s="6">
         <f>[1]Hoja1!O66</f>
@@ -13949,7 +13943,7 @@
         <f>[1]Hoja1!P66</f>
         <v>100</v>
       </c>
-      <c r="Q66" s="17">
+      <c r="Q66" s="6">
         <f>[1]Hoja1!Q66</f>
         <v>90</v>
       </c>
@@ -14017,7 +14011,7 @@
         <f>[1]Hoja1!P67</f>
         <v>0</v>
       </c>
-      <c r="Q67" s="17">
+      <c r="Q67" s="6">
         <f>[1]Hoja1!Q67</f>
         <v>0</v>
       </c>
@@ -14085,7 +14079,7 @@
         <f>[1]Hoja1!P68</f>
         <v>70</v>
       </c>
-      <c r="Q68" s="17">
+      <c r="Q68" s="6">
         <f>[1]Hoja1!Q68</f>
         <v>100</v>
       </c>
@@ -14153,7 +14147,7 @@
         <f>[1]Hoja1!P69</f>
         <v>65</v>
       </c>
-      <c r="Q69" s="17">
+      <c r="Q69" s="6">
         <f>[1]Hoja1!Q69</f>
         <v>80</v>
       </c>
@@ -14221,7 +14215,7 @@
         <f>[1]Hoja1!P70</f>
         <v>100</v>
       </c>
-      <c r="Q70" s="17">
+      <c r="Q70" s="6">
         <f>[1]Hoja1!Q70</f>
         <v>100</v>
       </c>
@@ -14289,7 +14283,7 @@
         <f>[1]Hoja1!P71</f>
         <v>100</v>
       </c>
-      <c r="Q71" s="17">
+      <c r="Q71" s="6">
         <f>[1]Hoja1!Q71</f>
         <v>0</v>
       </c>
@@ -14357,7 +14351,7 @@
         <f>[1]Hoja1!P72</f>
         <v>85</v>
       </c>
-      <c r="Q72" s="17">
+      <c r="Q72" s="6">
         <f>[1]Hoja1!Q72</f>
         <v>95</v>
       </c>
@@ -14425,7 +14419,7 @@
         <f>[1]Hoja1!P73</f>
         <v>70</v>
       </c>
-      <c r="Q73" s="17">
+      <c r="Q73" s="6">
         <f>[1]Hoja1!Q73</f>
         <v>0</v>
       </c>
@@ -14493,7 +14487,7 @@
         <f>[1]Hoja1!P74</f>
         <v>20</v>
       </c>
-      <c r="Q74" s="17">
+      <c r="Q74" s="6">
         <f>[1]Hoja1!Q74</f>
         <v>100</v>
       </c>
@@ -14561,7 +14555,7 @@
         <f>[1]Hoja1!P75</f>
         <v>0</v>
       </c>
-      <c r="Q75" s="17">
+      <c r="Q75" s="6">
         <f>[1]Hoja1!Q75</f>
         <v>0</v>
       </c>
@@ -14629,7 +14623,7 @@
         <f>[1]Hoja1!P76</f>
         <v>100</v>
       </c>
-      <c r="Q76" s="17">
+      <c r="Q76" s="6">
         <f>[1]Hoja1!Q76</f>
         <v>100</v>
       </c>
@@ -14697,7 +14691,7 @@
         <f>[1]Hoja1!P77</f>
         <v>0</v>
       </c>
-      <c r="Q77" s="48">
+      <c r="Q77" s="13">
         <f>[1]Hoja1!Q77</f>
         <v>0</v>
       </c>
